--- a/config/data/EnemyResistance.xlsx
+++ b/config/data/EnemyResistance.xlsx
@@ -1,103 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="EnemyResistance" sheetId="1" r:id="rId1"/>
+    <sheet name="EnemyResistance" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
-  <si>
-    <t>@table</t>
-  </si>
-  <si>
-    <t>EnemyResistance</t>
-  </si>
-  <si>
-    <t>@mode</t>
-  </si>
-  <si>
-    <t>list</t>
-  </si>
-  <si>
-    <t>@key</t>
-  </si>
-  <si>
-    <t>@scope</t>
-  </si>
-  <si>
-    <t>all</t>
-  </si>
-  <si>
-    <t>@schema</t>
-  </si>
-  <si>
-    <t>9a01aaa2e9f2c1f4</t>
-  </si>
-  <si>
-    <t>#name</t>
-  </si>
-  <si>
-    <t>variant_id</t>
-  </si>
-  <si>
-    <t>element</t>
-  </si>
-  <si>
-    <t>value_decimal</t>
-  </si>
-  <si>
-    <t>#field</t>
-  </si>
-  <si>
-    <t>#type</t>
-  </si>
-  <si>
-    <t>ref&lt;EnemyVariant.id&gt;</t>
-  </si>
-  <si>
-    <t>enum&lt;CombatElement&gt;</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>#scope</t>
-  </si>
-  <si>
-    <t>#input</t>
-  </si>
-  <si>
-    <t>length=1..32</t>
-  </si>
-  <si>
-    <t>#desc</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -116,13 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -410,106 +407,1276 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J81"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>21</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>EnemyResistance</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>@scope</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>9a01aaa2e9f2c1f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>variant_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>value_decimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>variant_id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>value_decimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ref&lt;EnemyVariant.id&gt;</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>enum&lt;CombatElement&gt;</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>#scope</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>length=1..32</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>101</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>101</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>101</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>101</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>101</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>102</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>102</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>102</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>102</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>103</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>103</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>103</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>103</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>103</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>104</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>104</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>104</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>104</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>104</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>105</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>105</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>105</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>105</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>106</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>106</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>106</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>106</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>107</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>107</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>107</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>107</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>108</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>108</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>108</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>108</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>109</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>109</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>109</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>109</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>109</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>110</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="n">
+        <v>110</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>110</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>110</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>110</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>111</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="n">
+        <v>111</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="n">
+        <v>111</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="n">
+        <v>111</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="n">
+        <v>95</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="n">
+        <v>95</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="n">
+        <v>95</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="n">
+        <v>95</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="n">
+        <v>96</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="n">
+        <v>96</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="n">
+        <v>96</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="n">
+        <v>96</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="n">
+        <v>97</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="n">
+        <v>97</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="n">
+        <v>97</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="n">
+        <v>97</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="n">
+        <v>97</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="n">
+        <v>98</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="n">
+        <v>98</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="n">
+        <v>98</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="n">
+        <v>98</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="n">
+        <v>99</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="n">
+        <v>99</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="n">
+        <v>99</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="n">
+        <v>99</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/config/data/EnemyResistance.xlsx
+++ b/config/data/EnemyResistance.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1679,6 +1679,66 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="B82" t="n">
+        <v>980001</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="n">
+        <v>980001</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="n">
+        <v>980001</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="n">
+        <v>980001</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyResistance.xlsx
+++ b/config/data/EnemyResistance.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1739,6 +1739,66 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="B86" t="n">
+        <v>990001</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="n">
+        <v>990001</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="n">
+        <v>990001</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="n">
+        <v>990001</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyResistance.xlsx
+++ b/config/data/EnemyResistance.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J89"/>
+  <dimension ref="A1:J93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1799,6 +1799,66 @@
         </is>
       </c>
     </row>
+    <row r="90">
+      <c r="B90" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyResistance.xlsx
+++ b/config/data/EnemyResistance.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J93"/>
+  <dimension ref="A1:J97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1859,6 +1859,66 @@
         </is>
       </c>
     </row>
+    <row r="94">
+      <c r="B94" t="n">
+        <v>1010001</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="n">
+        <v>1010001</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="n">
+        <v>1010001</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="n">
+        <v>1010001</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyResistance.xlsx
+++ b/config/data/EnemyResistance.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J97"/>
+  <dimension ref="A1:J101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1919,6 +1919,66 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="B98" t="n">
+        <v>1020001</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="n">
+        <v>1020001</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="n">
+        <v>1020001</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="n">
+        <v>1020001</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyResistance.xlsx
+++ b/config/data/EnemyResistance.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J101"/>
+  <dimension ref="A1:J105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1979,6 +1979,66 @@
         </is>
       </c>
     </row>
+    <row r="102">
+      <c r="B102" t="n">
+        <v>1030001</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="n">
+        <v>1030001</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" t="n">
+        <v>1030001</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="n">
+        <v>1030001</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyResistance.xlsx
+++ b/config/data/EnemyResistance.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J105"/>
+  <dimension ref="A1:J109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2039,6 +2039,66 @@
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="B106" t="n">
+        <v>1040001</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" t="n">
+        <v>1040001</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" t="n">
+        <v>1040001</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" t="n">
+        <v>1040001</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyResistance.xlsx
+++ b/config/data/EnemyResistance.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J109"/>
+  <dimension ref="A1:J113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2099,6 +2099,66 @@
         </is>
       </c>
     </row>
+    <row r="110">
+      <c r="B110" t="n">
+        <v>1050001</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" t="n">
+        <v>1050001</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" t="n">
+        <v>1050001</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" t="n">
+        <v>1050001</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyResistance.xlsx
+++ b/config/data/EnemyResistance.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J113"/>
+  <dimension ref="A1:J117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2159,6 +2159,66 @@
         </is>
       </c>
     </row>
+    <row r="114">
+      <c r="B114" t="n">
+        <v>1060001</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" t="n">
+        <v>1060001</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" t="n">
+        <v>1060001</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" t="n">
+        <v>1060001</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyResistance.xlsx
+++ b/config/data/EnemyResistance.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J117"/>
+  <dimension ref="A1:J121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2219,6 +2219,66 @@
         </is>
       </c>
     </row>
+    <row r="118">
+      <c r="B118" t="n">
+        <v>1070001</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" t="n">
+        <v>1070001</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" t="n">
+        <v>1070001</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" t="n">
+        <v>1070001</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyResistance.xlsx
+++ b/config/data/EnemyResistance.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J121"/>
+  <dimension ref="A1:J125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2279,6 +2279,66 @@
         </is>
       </c>
     </row>
+    <row r="122">
+      <c r="B122" t="n">
+        <v>1080001</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" t="n">
+        <v>1080001</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" t="n">
+        <v>1080001</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" t="n">
+        <v>1080001</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyResistance.xlsx
+++ b/config/data/EnemyResistance.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J125"/>
+  <dimension ref="A1:J167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1366,7 +1366,7 @@
     </row>
     <row r="61">
       <c r="B61" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1381,11 +1381,11 @@
     </row>
     <row r="62">
       <c r="B62" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1396,11 +1396,11 @@
     </row>
     <row r="63">
       <c r="B63" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1411,11 +1411,11 @@
     </row>
     <row r="64">
       <c r="B64" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1426,11 +1426,11 @@
     </row>
     <row r="65">
       <c r="B65" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1441,7 +1441,7 @@
     </row>
     <row r="66">
       <c r="B66" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -1450,13 +1450,13 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.6</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="B67" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -1465,13 +1465,13 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="B68" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -1480,32 +1480,32 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="B69" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="B70" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -1516,7 +1516,7 @@
     </row>
     <row r="71">
       <c r="B71" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -1531,11 +1531,11 @@
     </row>
     <row r="72">
       <c r="B72" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -1546,7 +1546,7 @@
     </row>
     <row r="73">
       <c r="B73" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -1561,26 +1561,26 @@
     </row>
     <row r="74">
       <c r="B74" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="B75" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -1591,7 +1591,7 @@
     </row>
     <row r="76">
       <c r="B76" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -1600,13 +1600,13 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="B77" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="B78" t="n">
-        <v>99</v>
+        <v>990001</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -1636,11 +1636,11 @@
     </row>
     <row r="79">
       <c r="B79" t="n">
-        <v>99</v>
+        <v>990001</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -1651,11 +1651,11 @@
     </row>
     <row r="80">
       <c r="B80" t="n">
-        <v>99</v>
+        <v>990001</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -1666,11 +1666,11 @@
     </row>
     <row r="81">
       <c r="B81" t="n">
-        <v>99</v>
+        <v>990001</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -1681,7 +1681,7 @@
     </row>
     <row r="82">
       <c r="B82" t="n">
-        <v>980001</v>
+        <v>1000001</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -1696,11 +1696,11 @@
     </row>
     <row r="83">
       <c r="B83" t="n">
-        <v>980001</v>
+        <v>1000001</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -1711,11 +1711,11 @@
     </row>
     <row r="84">
       <c r="B84" t="n">
-        <v>980001</v>
+        <v>1000001</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -1726,7 +1726,7 @@
     </row>
     <row r="85">
       <c r="B85" t="n">
-        <v>980001</v>
+        <v>1000001</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
     </row>
     <row r="86">
       <c r="B86" t="n">
-        <v>990001</v>
+        <v>1010001</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -1750,17 +1750,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="B87" t="n">
-        <v>990001</v>
+        <v>1010001</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -1771,11 +1771,11 @@
     </row>
     <row r="88">
       <c r="B88" t="n">
-        <v>990001</v>
+        <v>1010001</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -1786,7 +1786,7 @@
     </row>
     <row r="89">
       <c r="B89" t="n">
-        <v>990001</v>
+        <v>1010001</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -1801,11 +1801,11 @@
     </row>
     <row r="90">
       <c r="B90" t="n">
-        <v>1000001</v>
+        <v>1020001</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -1816,26 +1816,26 @@
     </row>
     <row r="91">
       <c r="B91" t="n">
-        <v>1000001</v>
+        <v>1020001</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="B92" t="n">
-        <v>1000001</v>
+        <v>1020001</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -1846,11 +1846,11 @@
     </row>
     <row r="93">
       <c r="B93" t="n">
-        <v>1000001</v>
+        <v>1020001</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -1861,22 +1861,22 @@
     </row>
     <row r="94">
       <c r="B94" t="n">
-        <v>1010001</v>
+        <v>1030001</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.6</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="B95" t="n">
-        <v>1010001</v>
+        <v>1030001</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -1891,22 +1891,22 @@
     </row>
     <row r="96">
       <c r="B96" t="n">
-        <v>1010001</v>
+        <v>1030001</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="B97" t="n">
-        <v>1010001</v>
+        <v>1030001</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -1915,13 +1915,13 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="B98" t="n">
-        <v>1020001</v>
+        <v>1040001</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
     </row>
     <row r="99">
       <c r="B99" t="n">
-        <v>1020001</v>
+        <v>1040001</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -1951,11 +1951,11 @@
     </row>
     <row r="100">
       <c r="B100" t="n">
-        <v>1020001</v>
+        <v>1040001</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -1966,11 +1966,11 @@
     </row>
     <row r="101">
       <c r="B101" t="n">
-        <v>1020001</v>
+        <v>1040001</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -1981,7 +1981,7 @@
     </row>
     <row r="102">
       <c r="B102" t="n">
-        <v>1030001</v>
+        <v>1050001</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -1990,13 +1990,13 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="B103" t="n">
-        <v>1030001</v>
+        <v>1050001</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -2011,41 +2011,41 @@
     </row>
     <row r="104">
       <c r="B104" t="n">
-        <v>1030001</v>
+        <v>1050001</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="B105" t="n">
-        <v>1030001</v>
+        <v>1050001</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="B106" t="n">
-        <v>1040001</v>
+        <v>1060001</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2056,26 +2056,26 @@
     </row>
     <row r="107">
       <c r="B107" t="n">
-        <v>1040001</v>
+        <v>1060001</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="B108" t="n">
-        <v>1040001</v>
+        <v>1060001</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -2086,11 +2086,11 @@
     </row>
     <row r="109">
       <c r="B109" t="n">
-        <v>1040001</v>
+        <v>1060001</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -2101,26 +2101,26 @@
     </row>
     <row r="110">
       <c r="B110" t="n">
-        <v>1050001</v>
+        <v>1070001</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="B111" t="n">
-        <v>1050001</v>
+        <v>1070001</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -2131,7 +2131,7 @@
     </row>
     <row r="112">
       <c r="B112" t="n">
-        <v>1050001</v>
+        <v>1070001</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -2140,17 +2140,17 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="B113" t="n">
-        <v>1050001</v>
+        <v>1070001</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -2161,7 +2161,7 @@
     </row>
     <row r="114">
       <c r="B114" t="n">
-        <v>1060001</v>
+        <v>1080001</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -2176,11 +2176,11 @@
     </row>
     <row r="115">
       <c r="B115" t="n">
-        <v>1060001</v>
+        <v>1080001</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -2191,7 +2191,7 @@
     </row>
     <row r="116">
       <c r="B116" t="n">
-        <v>1060001</v>
+        <v>1080001</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
     </row>
     <row r="117">
       <c r="B117" t="n">
-        <v>1060001</v>
+        <v>1080001</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
     </row>
     <row r="118">
       <c r="B118" t="n">
-        <v>1070001</v>
+        <v>1090005</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -2236,11 +2236,11 @@
     </row>
     <row r="119">
       <c r="B119" t="n">
-        <v>1070001</v>
+        <v>1090006</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -2251,26 +2251,26 @@
     </row>
     <row r="120">
       <c r="B120" t="n">
-        <v>1070001</v>
+        <v>1090008</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="B121" t="n">
-        <v>1070001</v>
+        <v>1090009</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -2281,11 +2281,11 @@
     </row>
     <row r="122">
       <c r="B122" t="n">
-        <v>1080001</v>
+        <v>1090010</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -2296,11 +2296,11 @@
     </row>
     <row r="123">
       <c r="B123" t="n">
-        <v>1080001</v>
+        <v>1090012</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -2311,11 +2311,11 @@
     </row>
     <row r="124">
       <c r="B124" t="n">
-        <v>1080001</v>
+        <v>95</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -2326,14 +2326,644 @@
     </row>
     <row r="125">
       <c r="B125" t="n">
-        <v>1080001</v>
+        <v>96</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" t="n">
+        <v>1090004</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" t="n">
+        <v>1090005</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" t="n">
+        <v>1090006</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" t="n">
+        <v>1090008</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" t="n">
+        <v>1090009</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" t="n">
+        <v>1090012</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" t="n">
+        <v>96</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" t="n">
+        <v>1090002</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" t="n">
+        <v>1090003</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" t="n">
+        <v>1090005</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" t="n">
+        <v>1090011</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" t="n">
+        <v>1090012</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" t="n">
+        <v>95</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" t="n">
+        <v>1090006</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" t="n">
+        <v>96</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" t="n">
+        <v>1090002</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" t="n">
+        <v>1090003</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" t="n">
+        <v>1090004</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" t="n">
+        <v>1090005</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" t="n">
+        <v>1090002</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" t="n">
+        <v>1090003</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" t="n">
+        <v>1090004</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" t="n">
+        <v>1090006</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" t="n">
+        <v>1090009</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" t="n">
+        <v>1090010</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" t="n">
+        <v>1090011</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" t="n">
+        <v>95</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" t="n">
+        <v>96</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" t="n">
+        <v>1090002</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
           <t>Quantum</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" t="n">
+        <v>1090003</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" t="n">
+        <v>1090004</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" t="n">
+        <v>1090008</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" t="n">
+        <v>1090009</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" t="n">
+        <v>1090010</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" t="n">
+        <v>1090011</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" t="n">
+        <v>1090012</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" t="n">
+        <v>1090005</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" t="n">
+        <v>1090008</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" t="n">
+        <v>1090010</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" t="n">
+        <v>1090011</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" t="n">
+        <v>1090012</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" t="n">
+        <v>95</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>

--- a/config/data/EnemyResistance.xlsx
+++ b/config/data/EnemyResistance.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J167"/>
+  <dimension ref="A1:J206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -571,7 +571,7 @@
     </row>
     <row r="8">
       <c r="B8" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -586,26 +586,26 @@
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -616,11 +616,11 @@
     </row>
     <row r="11">
       <c r="B11" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -646,11 +646,11 @@
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -661,11 +661,11 @@
     </row>
     <row r="14">
       <c r="B14" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -676,11 +676,11 @@
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -691,11 +691,11 @@
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -706,7 +706,7 @@
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -715,17 +715,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -736,11 +736,11 @@
     </row>
     <row r="19">
       <c r="B19" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -751,11 +751,11 @@
     </row>
     <row r="20">
       <c r="B20" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -770,37 +770,37 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -811,11 +811,11 @@
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -826,11 +826,11 @@
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -845,22 +845,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -871,11 +871,11 @@
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -886,11 +886,11 @@
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -901,11 +901,11 @@
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -916,26 +916,26 @@
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -946,11 +946,11 @@
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -961,11 +961,11 @@
     </row>
     <row r="34">
       <c r="B34" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -976,22 +976,22 @@
     </row>
     <row r="35">
       <c r="B35" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
     </row>
     <row r="37">
       <c r="B37" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1021,26 +1021,26 @@
     </row>
     <row r="38">
       <c r="B38" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1051,11 +1051,11 @@
     </row>
     <row r="40">
       <c r="B40" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1066,7 +1066,7 @@
     </row>
     <row r="41">
       <c r="B41" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
     </row>
     <row r="42">
       <c r="B42" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1090,17 +1090,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1111,11 +1111,11 @@
     </row>
     <row r="44">
       <c r="B44" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1126,7 +1126,7 @@
     </row>
     <row r="45">
       <c r="B45" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1141,11 +1141,11 @@
     </row>
     <row r="46">
       <c r="B46" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1171,11 +1171,11 @@
     </row>
     <row r="48">
       <c r="B48" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1186,11 +1186,11 @@
     </row>
     <row r="49">
       <c r="B49" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1201,11 +1201,11 @@
     </row>
     <row r="50">
       <c r="B50" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1216,11 +1216,11 @@
     </row>
     <row r="51">
       <c r="B51" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1246,11 +1246,11 @@
     </row>
     <row r="53">
       <c r="B53" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1261,11 +1261,11 @@
     </row>
     <row r="54">
       <c r="B54" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1276,11 +1276,11 @@
     </row>
     <row r="55">
       <c r="B55" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1291,11 +1291,11 @@
     </row>
     <row r="56">
       <c r="B56" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1306,26 +1306,26 @@
     </row>
     <row r="57">
       <c r="B57" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1336,41 +1336,41 @@
     </row>
     <row r="59">
       <c r="B59" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" t="n">
-        <v>97</v>
+        <v>980001</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1381,11 +1381,11 @@
     </row>
     <row r="62">
       <c r="B62" t="n">
-        <v>97</v>
+        <v>980001</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1396,11 +1396,11 @@
     </row>
     <row r="63">
       <c r="B63" t="n">
-        <v>97</v>
+        <v>980001</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1411,11 +1411,11 @@
     </row>
     <row r="64">
       <c r="B64" t="n">
-        <v>97</v>
+        <v>980001</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1426,11 +1426,11 @@
     </row>
     <row r="65">
       <c r="B65" t="n">
-        <v>97</v>
+        <v>990001</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1441,26 +1441,26 @@
     </row>
     <row r="66">
       <c r="B66" t="n">
-        <v>98</v>
+        <v>990001</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="B67" t="n">
-        <v>98</v>
+        <v>990001</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -1471,41 +1471,41 @@
     </row>
     <row r="68">
       <c r="B68" t="n">
-        <v>98</v>
+        <v>990001</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="B69" t="n">
-        <v>98</v>
+        <v>1000001</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="B70" t="n">
-        <v>99</v>
+        <v>1000001</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -1516,11 +1516,11 @@
     </row>
     <row r="71">
       <c r="B71" t="n">
-        <v>99</v>
+        <v>1000001</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -1531,11 +1531,11 @@
     </row>
     <row r="72">
       <c r="B72" t="n">
-        <v>99</v>
+        <v>1000001</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -1546,22 +1546,22 @@
     </row>
     <row r="73">
       <c r="B73" t="n">
-        <v>99</v>
+        <v>1010001</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="B74" t="n">
-        <v>980001</v>
+        <v>1010001</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
     </row>
     <row r="75">
       <c r="B75" t="n">
-        <v>980001</v>
+        <v>1010001</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -1591,11 +1591,11 @@
     </row>
     <row r="76">
       <c r="B76" t="n">
-        <v>980001</v>
+        <v>1010001</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -1606,11 +1606,11 @@
     </row>
     <row r="77">
       <c r="B77" t="n">
-        <v>980001</v>
+        <v>1020001</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -1621,22 +1621,22 @@
     </row>
     <row r="78">
       <c r="B78" t="n">
-        <v>990001</v>
+        <v>1020001</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="B79" t="n">
-        <v>990001</v>
+        <v>1020001</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
     </row>
     <row r="80">
       <c r="B80" t="n">
-        <v>990001</v>
+        <v>1020001</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -1666,22 +1666,22 @@
     </row>
     <row r="81">
       <c r="B81" t="n">
-        <v>990001</v>
+        <v>1030001</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.6</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="B82" t="n">
-        <v>1000001</v>
+        <v>1030001</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
     </row>
     <row r="83">
       <c r="B83" t="n">
-        <v>1000001</v>
+        <v>1030001</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -1705,32 +1705,32 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="B84" t="n">
-        <v>1000001</v>
+        <v>1030001</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="B85" t="n">
-        <v>1000001</v>
+        <v>1040001</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -1741,11 +1741,11 @@
     </row>
     <row r="86">
       <c r="B86" t="n">
-        <v>1010001</v>
+        <v>1040001</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -1756,11 +1756,11 @@
     </row>
     <row r="87">
       <c r="B87" t="n">
-        <v>1010001</v>
+        <v>1040001</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -1771,11 +1771,11 @@
     </row>
     <row r="88">
       <c r="B88" t="n">
-        <v>1010001</v>
+        <v>1040001</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -1786,26 +1786,26 @@
     </row>
     <row r="89">
       <c r="B89" t="n">
-        <v>1010001</v>
+        <v>1050001</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="B90" t="n">
-        <v>1020001</v>
+        <v>1050001</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -1816,22 +1816,22 @@
     </row>
     <row r="91">
       <c r="B91" t="n">
-        <v>1020001</v>
+        <v>1050001</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="B92" t="n">
-        <v>1020001</v>
+        <v>1050001</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -1846,11 +1846,11 @@
     </row>
     <row r="93">
       <c r="B93" t="n">
-        <v>1020001</v>
+        <v>1060001</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -1861,26 +1861,26 @@
     </row>
     <row r="94">
       <c r="B94" t="n">
-        <v>1030001</v>
+        <v>1060001</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="B95" t="n">
-        <v>1030001</v>
+        <v>1060001</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -1891,41 +1891,41 @@
     </row>
     <row r="96">
       <c r="B96" t="n">
-        <v>1030001</v>
+        <v>1060001</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="B97" t="n">
-        <v>1030001</v>
+        <v>1070001</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="B98" t="n">
-        <v>1040001</v>
+        <v>1070001</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -1936,11 +1936,11 @@
     </row>
     <row r="99">
       <c r="B99" t="n">
-        <v>1040001</v>
+        <v>1070001</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -1951,7 +1951,7 @@
     </row>
     <row r="100">
       <c r="B100" t="n">
-        <v>1040001</v>
+        <v>1070001</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -1966,11 +1966,11 @@
     </row>
     <row r="101">
       <c r="B101" t="n">
-        <v>1040001</v>
+        <v>1080001</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -1981,26 +1981,26 @@
     </row>
     <row r="102">
       <c r="B102" t="n">
-        <v>1050001</v>
+        <v>1080001</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="B103" t="n">
-        <v>1050001</v>
+        <v>1080001</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2011,11 +2011,11 @@
     </row>
     <row r="104">
       <c r="B104" t="n">
-        <v>1050001</v>
+        <v>1080001</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -2026,11 +2026,11 @@
     </row>
     <row r="105">
       <c r="B105" t="n">
-        <v>1050001</v>
+        <v>1090005</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -2041,11 +2041,11 @@
     </row>
     <row r="106">
       <c r="B106" t="n">
-        <v>1060001</v>
+        <v>1090006</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2056,11 +2056,11 @@
     </row>
     <row r="107">
       <c r="B107" t="n">
-        <v>1060001</v>
+        <v>1090008</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -2071,11 +2071,11 @@
     </row>
     <row r="108">
       <c r="B108" t="n">
-        <v>1060001</v>
+        <v>1090009</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -2086,11 +2086,11 @@
     </row>
     <row r="109">
       <c r="B109" t="n">
-        <v>1060001</v>
+        <v>1090010</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -2101,7 +2101,7 @@
     </row>
     <row r="110">
       <c r="B110" t="n">
-        <v>1070001</v>
+        <v>1090012</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -2116,11 +2116,11 @@
     </row>
     <row r="111">
       <c r="B111" t="n">
-        <v>1070001</v>
+        <v>95</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -2131,26 +2131,26 @@
     </row>
     <row r="112">
       <c r="B112" t="n">
-        <v>1070001</v>
+        <v>96</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="B113" t="n">
-        <v>1070001</v>
+        <v>1090004</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -2161,7 +2161,7 @@
     </row>
     <row r="114">
       <c r="B114" t="n">
-        <v>1080001</v>
+        <v>1090005</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -2176,11 +2176,11 @@
     </row>
     <row r="115">
       <c r="B115" t="n">
-        <v>1080001</v>
+        <v>1090006</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -2191,11 +2191,11 @@
     </row>
     <row r="116">
       <c r="B116" t="n">
-        <v>1080001</v>
+        <v>1090008</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -2206,11 +2206,11 @@
     </row>
     <row r="117">
       <c r="B117" t="n">
-        <v>1080001</v>
+        <v>1090009</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -2221,11 +2221,11 @@
     </row>
     <row r="118">
       <c r="B118" t="n">
-        <v>1090005</v>
+        <v>1090012</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -2236,11 +2236,11 @@
     </row>
     <row r="119">
       <c r="B119" t="n">
-        <v>1090006</v>
+        <v>96</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -2251,11 +2251,11 @@
     </row>
     <row r="120">
       <c r="B120" t="n">
-        <v>1090008</v>
+        <v>1090002</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -2266,11 +2266,11 @@
     </row>
     <row r="121">
       <c r="B121" t="n">
-        <v>1090009</v>
+        <v>1090003</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -2281,11 +2281,11 @@
     </row>
     <row r="122">
       <c r="B122" t="n">
-        <v>1090010</v>
+        <v>1090005</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -2296,11 +2296,11 @@
     </row>
     <row r="123">
       <c r="B123" t="n">
-        <v>1090012</v>
+        <v>1090011</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -2311,11 +2311,11 @@
     </row>
     <row r="124">
       <c r="B124" t="n">
-        <v>95</v>
+        <v>1090012</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -2326,11 +2326,11 @@
     </row>
     <row r="125">
       <c r="B125" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -2341,41 +2341,41 @@
     </row>
     <row r="126">
       <c r="B126" t="n">
-        <v>1090004</v>
+        <v>1090006</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="B127" t="n">
-        <v>1090005</v>
+        <v>96</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="B128" t="n">
-        <v>1090006</v>
+        <v>1090002</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -2386,11 +2386,11 @@
     </row>
     <row r="129">
       <c r="B129" t="n">
-        <v>1090008</v>
+        <v>1090003</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -2401,11 +2401,11 @@
     </row>
     <row r="130">
       <c r="B130" t="n">
-        <v>1090009</v>
+        <v>1090004</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -2416,11 +2416,11 @@
     </row>
     <row r="131">
       <c r="B131" t="n">
-        <v>1090012</v>
+        <v>1090005</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -2431,11 +2431,11 @@
     </row>
     <row r="132">
       <c r="B132" t="n">
-        <v>96</v>
+        <v>1090002</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -2446,11 +2446,11 @@
     </row>
     <row r="133">
       <c r="B133" t="n">
-        <v>1090002</v>
+        <v>1090003</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -2461,11 +2461,11 @@
     </row>
     <row r="134">
       <c r="B134" t="n">
-        <v>1090003</v>
+        <v>1090004</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -2476,11 +2476,11 @@
     </row>
     <row r="135">
       <c r="B135" t="n">
-        <v>1090005</v>
+        <v>1090006</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -2491,11 +2491,11 @@
     </row>
     <row r="136">
       <c r="B136" t="n">
-        <v>1090011</v>
+        <v>1090009</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -2506,11 +2506,11 @@
     </row>
     <row r="137">
       <c r="B137" t="n">
-        <v>1090012</v>
+        <v>1090010</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -2521,11 +2521,11 @@
     </row>
     <row r="138">
       <c r="B138" t="n">
-        <v>95</v>
+        <v>1090011</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -2536,16 +2536,16 @@
     </row>
     <row r="139">
       <c r="B139" t="n">
-        <v>1090006</v>
+        <v>95</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2555,12 +2555,12 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -2611,11 +2611,11 @@
     </row>
     <row r="144">
       <c r="B144" t="n">
-        <v>1090005</v>
+        <v>1090008</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -2626,11 +2626,11 @@
     </row>
     <row r="145">
       <c r="B145" t="n">
-        <v>1090002</v>
+        <v>1090009</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -2641,11 +2641,11 @@
     </row>
     <row r="146">
       <c r="B146" t="n">
-        <v>1090003</v>
+        <v>1090010</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -2656,11 +2656,11 @@
     </row>
     <row r="147">
       <c r="B147" t="n">
-        <v>1090004</v>
+        <v>1090011</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -2671,11 +2671,11 @@
     </row>
     <row r="148">
       <c r="B148" t="n">
-        <v>1090006</v>
+        <v>1090012</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -2686,11 +2686,11 @@
     </row>
     <row r="149">
       <c r="B149" t="n">
-        <v>1090009</v>
+        <v>1090005</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -2701,11 +2701,11 @@
     </row>
     <row r="150">
       <c r="B150" t="n">
-        <v>1090010</v>
+        <v>1090008</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -2716,11 +2716,11 @@
     </row>
     <row r="151">
       <c r="B151" t="n">
-        <v>1090011</v>
+        <v>1090010</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -2731,11 +2731,11 @@
     </row>
     <row r="152">
       <c r="B152" t="n">
-        <v>95</v>
+        <v>1090011</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -2746,11 +2746,11 @@
     </row>
     <row r="153">
       <c r="B153" t="n">
-        <v>96</v>
+        <v>1090012</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -2761,11 +2761,11 @@
     </row>
     <row r="154">
       <c r="B154" t="n">
-        <v>1090002</v>
+        <v>95</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -2776,11 +2776,11 @@
     </row>
     <row r="155">
       <c r="B155" t="n">
-        <v>1090003</v>
+        <v>100</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -2791,11 +2791,11 @@
     </row>
     <row r="156">
       <c r="B156" t="n">
-        <v>1090004</v>
+        <v>1100002</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -2806,11 +2806,11 @@
     </row>
     <row r="157">
       <c r="B157" t="n">
-        <v>1090008</v>
+        <v>1100006</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -2821,11 +2821,11 @@
     </row>
     <row r="158">
       <c r="B158" t="n">
-        <v>1090009</v>
+        <v>1100007</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -2836,11 +2836,11 @@
     </row>
     <row r="159">
       <c r="B159" t="n">
-        <v>1090010</v>
+        <v>1100011</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -2851,11 +2851,11 @@
     </row>
     <row r="160">
       <c r="B160" t="n">
-        <v>1090011</v>
+        <v>1100012</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -2866,11 +2866,11 @@
     </row>
     <row r="161">
       <c r="B161" t="n">
-        <v>1090012</v>
+        <v>97</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -2881,11 +2881,11 @@
     </row>
     <row r="162">
       <c r="B162" t="n">
-        <v>1090005</v>
+        <v>99</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -2896,11 +2896,11 @@
     </row>
     <row r="163">
       <c r="B163" t="n">
-        <v>1090008</v>
+        <v>1100003</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -2911,11 +2911,11 @@
     </row>
     <row r="164">
       <c r="B164" t="n">
-        <v>1090010</v>
+        <v>1100004</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -2926,11 +2926,11 @@
     </row>
     <row r="165">
       <c r="B165" t="n">
-        <v>1090011</v>
+        <v>1100006</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -2941,11 +2941,11 @@
     </row>
     <row r="166">
       <c r="B166" t="n">
-        <v>1090012</v>
+        <v>1100009</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -2956,14 +2956,599 @@
     </row>
     <row r="167">
       <c r="B167" t="n">
-        <v>95</v>
+        <v>1100010</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" t="n">
+        <v>1100011</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" t="n">
+        <v>1100012</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" t="n">
+        <v>97</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" t="n">
+        <v>1100002</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" t="n">
+        <v>1100004</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" t="n">
+        <v>1100009</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" t="n">
+        <v>1100010</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" t="n">
+        <v>1100012</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" t="n">
+        <v>97</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" t="n">
+        <v>99</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" t="n">
+        <v>100</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" t="n">
+        <v>1100002</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" t="n">
+        <v>1100003</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" t="n">
+        <v>1100007</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" t="n">
+        <v>99</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" t="n">
+        <v>1100006</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="B184" t="n">
+        <v>100</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" t="n">
+        <v>1100002</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" t="n">
+        <v>1100003</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" t="n">
+        <v>1100004</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" t="n">
+        <v>1100007</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" t="n">
+        <v>1100009</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" t="n">
+        <v>1100010</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="B191" t="n">
+        <v>1100011</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="B192" t="n">
+        <v>97</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="B193" t="n">
+        <v>100</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="B194" t="n">
+        <v>1100002</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="B195" t="n">
+        <v>1100003</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="B196" t="n">
+        <v>1100004</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="B197" t="n">
+        <v>1100006</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="B198" t="n">
+        <v>1100007</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="B199" t="n">
+        <v>1100009</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="B200" t="n">
+        <v>1100010</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="B201" t="n">
+        <v>1100011</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="B202" t="n">
+        <v>1100012</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="B203" t="n">
+        <v>97</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="B204" t="n">
+        <v>99</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="B205" t="n">
+        <v>1100006</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
           <t>Wind</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr">
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="B206" t="n">
+        <v>1100011</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>

--- a/config/data/EnemyResistance.xlsx
+++ b/config/data/EnemyResistance.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J206"/>
+  <dimension ref="A1:J246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -646,11 +646,11 @@
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -661,11 +661,11 @@
     </row>
     <row r="14">
       <c r="B14" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -676,7 +676,7 @@
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -721,11 +721,11 @@
     </row>
     <row r="18">
       <c r="B18" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -736,11 +736,11 @@
     </row>
     <row r="19">
       <c r="B19" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -751,7 +751,7 @@
     </row>
     <row r="20">
       <c r="B20" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -766,11 +766,11 @@
     </row>
     <row r="21">
       <c r="B21" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -781,26 +781,26 @@
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -811,26 +811,26 @@
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -841,11 +841,11 @@
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -856,11 +856,11 @@
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -871,11 +871,11 @@
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -886,11 +886,11 @@
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -901,11 +901,11 @@
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -916,26 +916,26 @@
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -946,11 +946,11 @@
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -961,11 +961,11 @@
     </row>
     <row r="34">
       <c r="B34" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -976,11 +976,11 @@
     </row>
     <row r="35">
       <c r="B35" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -991,11 +991,11 @@
     </row>
     <row r="36">
       <c r="B36" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1006,11 +1006,11 @@
     </row>
     <row r="37">
       <c r="B37" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1021,7 +1021,7 @@
     </row>
     <row r="38">
       <c r="B38" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1030,13 +1030,13 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1051,11 +1051,11 @@
     </row>
     <row r="40">
       <c r="B40" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1066,11 +1066,11 @@
     </row>
     <row r="41">
       <c r="B41" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1081,11 +1081,11 @@
     </row>
     <row r="42">
       <c r="B42" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1096,7 +1096,7 @@
     </row>
     <row r="43">
       <c r="B43" t="n">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="n">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1126,7 +1126,7 @@
     </row>
     <row r="45">
       <c r="B45" t="n">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1135,32 +1135,32 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="n">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" t="n">
-        <v>109</v>
+        <v>980001</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1171,11 +1171,11 @@
     </row>
     <row r="48">
       <c r="B48" t="n">
-        <v>110</v>
+        <v>980001</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1186,11 +1186,11 @@
     </row>
     <row r="49">
       <c r="B49" t="n">
-        <v>110</v>
+        <v>980001</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1201,11 +1201,11 @@
     </row>
     <row r="50">
       <c r="B50" t="n">
-        <v>110</v>
+        <v>980001</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1216,11 +1216,11 @@
     </row>
     <row r="51">
       <c r="B51" t="n">
-        <v>110</v>
+        <v>990001</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1231,11 +1231,11 @@
     </row>
     <row r="52">
       <c r="B52" t="n">
-        <v>110</v>
+        <v>990001</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1246,11 +1246,11 @@
     </row>
     <row r="53">
       <c r="B53" t="n">
-        <v>111</v>
+        <v>990001</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1261,11 +1261,11 @@
     </row>
     <row r="54">
       <c r="B54" t="n">
-        <v>111</v>
+        <v>990001</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1276,11 +1276,11 @@
     </row>
     <row r="55">
       <c r="B55" t="n">
-        <v>111</v>
+        <v>1000001</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1291,11 +1291,11 @@
     </row>
     <row r="56">
       <c r="B56" t="n">
-        <v>111</v>
+        <v>1000001</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1306,26 +1306,26 @@
     </row>
     <row r="57">
       <c r="B57" t="n">
-        <v>98</v>
+        <v>1000001</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" t="n">
-        <v>98</v>
+        <v>1000001</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1336,11 +1336,11 @@
     </row>
     <row r="59">
       <c r="B59" t="n">
-        <v>98</v>
+        <v>1010001</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1351,26 +1351,26 @@
     </row>
     <row r="60">
       <c r="B60" t="n">
-        <v>98</v>
+        <v>1010001</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" t="n">
-        <v>980001</v>
+        <v>1010001</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1381,11 +1381,11 @@
     </row>
     <row r="62">
       <c r="B62" t="n">
-        <v>980001</v>
+        <v>1010001</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1396,11 +1396,11 @@
     </row>
     <row r="63">
       <c r="B63" t="n">
-        <v>980001</v>
+        <v>1020001</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1411,26 +1411,26 @@
     </row>
     <row r="64">
       <c r="B64" t="n">
-        <v>980001</v>
+        <v>1020001</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" t="n">
-        <v>990001</v>
+        <v>1020001</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1441,11 +1441,11 @@
     </row>
     <row r="66">
       <c r="B66" t="n">
-        <v>990001</v>
+        <v>1020001</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -1456,26 +1456,26 @@
     </row>
     <row r="67">
       <c r="B67" t="n">
-        <v>990001</v>
+        <v>1030001</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.6</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="B68" t="n">
-        <v>990001</v>
+        <v>1030001</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -1486,41 +1486,41 @@
     </row>
     <row r="69">
       <c r="B69" t="n">
-        <v>1000001</v>
+        <v>1030001</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="B70" t="n">
-        <v>1000001</v>
+        <v>1030001</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="B71" t="n">
-        <v>1000001</v>
+        <v>1040001</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -1531,41 +1531,41 @@
     </row>
     <row r="72">
       <c r="B72" t="n">
-        <v>1000001</v>
+        <v>1040001</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="B73" t="n">
-        <v>1010001</v>
+        <v>1040001</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="B74" t="n">
-        <v>1010001</v>
+        <v>1040001</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -1576,26 +1576,26 @@
     </row>
     <row r="75">
       <c r="B75" t="n">
-        <v>1010001</v>
+        <v>1050001</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="B76" t="n">
-        <v>1010001</v>
+        <v>1050001</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -1606,11 +1606,11 @@
     </row>
     <row r="77">
       <c r="B77" t="n">
-        <v>1020001</v>
+        <v>1050001</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -1621,26 +1621,26 @@
     </row>
     <row r="78">
       <c r="B78" t="n">
-        <v>1020001</v>
+        <v>1050001</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="B79" t="n">
-        <v>1020001</v>
+        <v>1060001</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -1651,11 +1651,11 @@
     </row>
     <row r="80">
       <c r="B80" t="n">
-        <v>1020001</v>
+        <v>1060001</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -1666,26 +1666,26 @@
     </row>
     <row r="81">
       <c r="B81" t="n">
-        <v>1030001</v>
+        <v>1060001</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="B82" t="n">
-        <v>1030001</v>
+        <v>1060001</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -1696,71 +1696,71 @@
     </row>
     <row r="83">
       <c r="B83" t="n">
-        <v>1030001</v>
+        <v>1070001</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="B84" t="n">
-        <v>1030001</v>
+        <v>1070001</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="B85" t="n">
-        <v>1040001</v>
+        <v>1070001</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="B86" t="n">
-        <v>1040001</v>
+        <v>1070001</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="B87" t="n">
-        <v>1040001</v>
+        <v>1080001</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -1771,11 +1771,11 @@
     </row>
     <row r="88">
       <c r="B88" t="n">
-        <v>1040001</v>
+        <v>1080001</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -1786,26 +1786,26 @@
     </row>
     <row r="89">
       <c r="B89" t="n">
-        <v>1050001</v>
+        <v>1080001</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="B90" t="n">
-        <v>1050001</v>
+        <v>1080001</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -1816,11 +1816,11 @@
     </row>
     <row r="91">
       <c r="B91" t="n">
-        <v>1050001</v>
+        <v>1090005</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -1831,11 +1831,11 @@
     </row>
     <row r="92">
       <c r="B92" t="n">
-        <v>1050001</v>
+        <v>1090006</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -1846,11 +1846,11 @@
     </row>
     <row r="93">
       <c r="B93" t="n">
-        <v>1060001</v>
+        <v>1090008</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -1861,11 +1861,11 @@
     </row>
     <row r="94">
       <c r="B94" t="n">
-        <v>1060001</v>
+        <v>1090009</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -1876,11 +1876,11 @@
     </row>
     <row r="95">
       <c r="B95" t="n">
-        <v>1060001</v>
+        <v>1090010</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -1891,11 +1891,11 @@
     </row>
     <row r="96">
       <c r="B96" t="n">
-        <v>1060001</v>
+        <v>1090012</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -1906,7 +1906,7 @@
     </row>
     <row r="97">
       <c r="B97" t="n">
-        <v>1070001</v>
+        <v>95</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -1921,11 +1921,11 @@
     </row>
     <row r="98">
       <c r="B98" t="n">
-        <v>1070001</v>
+        <v>96</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -1936,26 +1936,26 @@
     </row>
     <row r="99">
       <c r="B99" t="n">
-        <v>1070001</v>
+        <v>1090004</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="B100" t="n">
-        <v>1070001</v>
+        <v>1090005</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -1966,7 +1966,7 @@
     </row>
     <row r="101">
       <c r="B101" t="n">
-        <v>1080001</v>
+        <v>1090006</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -1981,11 +1981,11 @@
     </row>
     <row r="102">
       <c r="B102" t="n">
-        <v>1080001</v>
+        <v>1090008</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -1996,11 +1996,11 @@
     </row>
     <row r="103">
       <c r="B103" t="n">
-        <v>1080001</v>
+        <v>1090009</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2011,11 +2011,11 @@
     </row>
     <row r="104">
       <c r="B104" t="n">
-        <v>1080001</v>
+        <v>1090012</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -2026,11 +2026,11 @@
     </row>
     <row r="105">
       <c r="B105" t="n">
-        <v>1090005</v>
+        <v>96</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -2041,11 +2041,11 @@
     </row>
     <row r="106">
       <c r="B106" t="n">
-        <v>1090006</v>
+        <v>1090002</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2056,11 +2056,11 @@
     </row>
     <row r="107">
       <c r="B107" t="n">
-        <v>1090008</v>
+        <v>1090003</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -2071,11 +2071,11 @@
     </row>
     <row r="108">
       <c r="B108" t="n">
-        <v>1090009</v>
+        <v>1090005</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -2086,11 +2086,11 @@
     </row>
     <row r="109">
       <c r="B109" t="n">
-        <v>1090010</v>
+        <v>1090011</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -2131,41 +2131,41 @@
     </row>
     <row r="112">
       <c r="B112" t="n">
-        <v>96</v>
+        <v>1090006</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="B113" t="n">
-        <v>1090004</v>
+        <v>96</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="B114" t="n">
-        <v>1090005</v>
+        <v>1090002</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -2176,11 +2176,11 @@
     </row>
     <row r="115">
       <c r="B115" t="n">
-        <v>1090006</v>
+        <v>1090003</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -2191,11 +2191,11 @@
     </row>
     <row r="116">
       <c r="B116" t="n">
-        <v>1090008</v>
+        <v>1090004</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -2206,11 +2206,11 @@
     </row>
     <row r="117">
       <c r="B117" t="n">
-        <v>1090009</v>
+        <v>1090005</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -2221,11 +2221,11 @@
     </row>
     <row r="118">
       <c r="B118" t="n">
-        <v>1090012</v>
+        <v>1090002</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -2236,11 +2236,11 @@
     </row>
     <row r="119">
       <c r="B119" t="n">
-        <v>96</v>
+        <v>1090003</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -2251,11 +2251,11 @@
     </row>
     <row r="120">
       <c r="B120" t="n">
-        <v>1090002</v>
+        <v>1090004</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -2266,11 +2266,11 @@
     </row>
     <row r="121">
       <c r="B121" t="n">
-        <v>1090003</v>
+        <v>1090006</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -2281,11 +2281,11 @@
     </row>
     <row r="122">
       <c r="B122" t="n">
-        <v>1090005</v>
+        <v>1090009</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -2296,11 +2296,11 @@
     </row>
     <row r="123">
       <c r="B123" t="n">
-        <v>1090011</v>
+        <v>1090010</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -2311,11 +2311,11 @@
     </row>
     <row r="124">
       <c r="B124" t="n">
-        <v>1090012</v>
+        <v>1090011</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -2341,41 +2341,41 @@
     </row>
     <row r="126">
       <c r="B126" t="n">
-        <v>1090006</v>
+        <v>96</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="B127" t="n">
-        <v>96</v>
+        <v>1090002</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="B128" t="n">
-        <v>1090002</v>
+        <v>1090003</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -2386,11 +2386,11 @@
     </row>
     <row r="129">
       <c r="B129" t="n">
-        <v>1090003</v>
+        <v>1090004</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -2401,11 +2401,11 @@
     </row>
     <row r="130">
       <c r="B130" t="n">
-        <v>1090004</v>
+        <v>1090008</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -2416,11 +2416,11 @@
     </row>
     <row r="131">
       <c r="B131" t="n">
-        <v>1090005</v>
+        <v>1090009</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -2431,11 +2431,11 @@
     </row>
     <row r="132">
       <c r="B132" t="n">
-        <v>1090002</v>
+        <v>1090010</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -2446,11 +2446,11 @@
     </row>
     <row r="133">
       <c r="B133" t="n">
-        <v>1090003</v>
+        <v>1090011</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -2461,11 +2461,11 @@
     </row>
     <row r="134">
       <c r="B134" t="n">
-        <v>1090004</v>
+        <v>1090012</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -2476,11 +2476,11 @@
     </row>
     <row r="135">
       <c r="B135" t="n">
-        <v>1090006</v>
+        <v>1090005</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -2491,11 +2491,11 @@
     </row>
     <row r="136">
       <c r="B136" t="n">
-        <v>1090009</v>
+        <v>1090008</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -2536,11 +2536,11 @@
     </row>
     <row r="139">
       <c r="B139" t="n">
-        <v>95</v>
+        <v>1090012</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -2551,11 +2551,11 @@
     </row>
     <row r="140">
       <c r="B140" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -2566,11 +2566,11 @@
     </row>
     <row r="141">
       <c r="B141" t="n">
-        <v>1090002</v>
+        <v>100</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -2581,11 +2581,11 @@
     </row>
     <row r="142">
       <c r="B142" t="n">
-        <v>1090003</v>
+        <v>1100002</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -2596,11 +2596,11 @@
     </row>
     <row r="143">
       <c r="B143" t="n">
-        <v>1090004</v>
+        <v>1100006</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -2611,11 +2611,11 @@
     </row>
     <row r="144">
       <c r="B144" t="n">
-        <v>1090008</v>
+        <v>1100007</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -2626,11 +2626,11 @@
     </row>
     <row r="145">
       <c r="B145" t="n">
-        <v>1090009</v>
+        <v>1100011</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -2641,11 +2641,11 @@
     </row>
     <row r="146">
       <c r="B146" t="n">
-        <v>1090010</v>
+        <v>1100012</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -2656,11 +2656,11 @@
     </row>
     <row r="147">
       <c r="B147" t="n">
-        <v>1090011</v>
+        <v>97</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -2671,11 +2671,11 @@
     </row>
     <row r="148">
       <c r="B148" t="n">
-        <v>1090012</v>
+        <v>99</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -2686,11 +2686,11 @@
     </row>
     <row r="149">
       <c r="B149" t="n">
-        <v>1090005</v>
+        <v>1100003</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -2701,11 +2701,11 @@
     </row>
     <row r="150">
       <c r="B150" t="n">
-        <v>1090008</v>
+        <v>1100004</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -2716,11 +2716,11 @@
     </row>
     <row r="151">
       <c r="B151" t="n">
-        <v>1090010</v>
+        <v>1100006</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -2731,11 +2731,11 @@
     </row>
     <row r="152">
       <c r="B152" t="n">
-        <v>1090011</v>
+        <v>1100009</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -2746,11 +2746,11 @@
     </row>
     <row r="153">
       <c r="B153" t="n">
-        <v>1090012</v>
+        <v>1100010</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -2761,11 +2761,11 @@
     </row>
     <row r="154">
       <c r="B154" t="n">
-        <v>95</v>
+        <v>1100011</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -2776,11 +2776,11 @@
     </row>
     <row r="155">
       <c r="B155" t="n">
-        <v>100</v>
+        <v>1100012</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -2791,11 +2791,11 @@
     </row>
     <row r="156">
       <c r="B156" t="n">
-        <v>1100002</v>
+        <v>97</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -2806,11 +2806,11 @@
     </row>
     <row r="157">
       <c r="B157" t="n">
-        <v>1100006</v>
+        <v>1100002</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -2821,11 +2821,11 @@
     </row>
     <row r="158">
       <c r="B158" t="n">
-        <v>1100007</v>
+        <v>1100004</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -2836,11 +2836,11 @@
     </row>
     <row r="159">
       <c r="B159" t="n">
-        <v>1100011</v>
+        <v>1100009</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -2851,11 +2851,11 @@
     </row>
     <row r="160">
       <c r="B160" t="n">
-        <v>1100012</v>
+        <v>1100010</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -2866,11 +2866,11 @@
     </row>
     <row r="161">
       <c r="B161" t="n">
-        <v>97</v>
+        <v>1100012</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -2881,11 +2881,11 @@
     </row>
     <row r="162">
       <c r="B162" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -2896,11 +2896,11 @@
     </row>
     <row r="163">
       <c r="B163" t="n">
-        <v>1100003</v>
+        <v>99</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -2911,11 +2911,11 @@
     </row>
     <row r="164">
       <c r="B164" t="n">
-        <v>1100004</v>
+        <v>100</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -2926,11 +2926,11 @@
     </row>
     <row r="165">
       <c r="B165" t="n">
-        <v>1100006</v>
+        <v>1100002</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -2941,11 +2941,11 @@
     </row>
     <row r="166">
       <c r="B166" t="n">
-        <v>1100009</v>
+        <v>1100003</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -2956,11 +2956,11 @@
     </row>
     <row r="167">
       <c r="B167" t="n">
-        <v>1100010</v>
+        <v>1100007</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -2971,11 +2971,11 @@
     </row>
     <row r="168">
       <c r="B168" t="n">
-        <v>1100011</v>
+        <v>99</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -2986,26 +2986,26 @@
     </row>
     <row r="169">
       <c r="B169" t="n">
-        <v>1100012</v>
+        <v>1100006</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="B170" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -3031,11 +3031,11 @@
     </row>
     <row r="172">
       <c r="B172" t="n">
-        <v>1100004</v>
+        <v>1100003</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -3046,11 +3046,11 @@
     </row>
     <row r="173">
       <c r="B173" t="n">
-        <v>1100009</v>
+        <v>1100004</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -3061,11 +3061,11 @@
     </row>
     <row r="174">
       <c r="B174" t="n">
-        <v>1100010</v>
+        <v>1100007</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -3076,11 +3076,11 @@
     </row>
     <row r="175">
       <c r="B175" t="n">
-        <v>1100012</v>
+        <v>1100009</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -3091,11 +3091,11 @@
     </row>
     <row r="176">
       <c r="B176" t="n">
-        <v>97</v>
+        <v>1100010</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -3106,11 +3106,11 @@
     </row>
     <row r="177">
       <c r="B177" t="n">
-        <v>99</v>
+        <v>1100011</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -3121,11 +3121,11 @@
     </row>
     <row r="178">
       <c r="B178" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -3136,11 +3136,11 @@
     </row>
     <row r="179">
       <c r="B179" t="n">
-        <v>1100002</v>
+        <v>100</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -3151,11 +3151,11 @@
     </row>
     <row r="180">
       <c r="B180" t="n">
-        <v>1100003</v>
+        <v>1100002</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -3166,11 +3166,11 @@
     </row>
     <row r="181">
       <c r="B181" t="n">
-        <v>1100007</v>
+        <v>1100003</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -3181,11 +3181,11 @@
     </row>
     <row r="182">
       <c r="B182" t="n">
-        <v>99</v>
+        <v>1100004</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -3200,22 +3200,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="B184" t="n">
-        <v>100</v>
+        <v>1100007</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -3226,11 +3226,11 @@
     </row>
     <row r="185">
       <c r="B185" t="n">
-        <v>1100002</v>
+        <v>1100009</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -3241,11 +3241,11 @@
     </row>
     <row r="186">
       <c r="B186" t="n">
-        <v>1100003</v>
+        <v>1100010</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -3256,11 +3256,11 @@
     </row>
     <row r="187">
       <c r="B187" t="n">
-        <v>1100004</v>
+        <v>1100011</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -3271,11 +3271,11 @@
     </row>
     <row r="188">
       <c r="B188" t="n">
-        <v>1100007</v>
+        <v>1100012</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -3286,11 +3286,11 @@
     </row>
     <row r="189">
       <c r="B189" t="n">
-        <v>1100009</v>
+        <v>97</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -3301,11 +3301,11 @@
     </row>
     <row r="190">
       <c r="B190" t="n">
-        <v>1100010</v>
+        <v>99</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -3316,11 +3316,11 @@
     </row>
     <row r="191">
       <c r="B191" t="n">
-        <v>1100011</v>
+        <v>1100006</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -3331,11 +3331,11 @@
     </row>
     <row r="192">
       <c r="B192" t="n">
-        <v>97</v>
+        <v>1100011</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -3346,11 +3346,11 @@
     </row>
     <row r="193">
       <c r="B193" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -3361,11 +3361,11 @@
     </row>
     <row r="194">
       <c r="B194" t="n">
-        <v>1100002</v>
+        <v>1110001</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -3376,11 +3376,11 @@
     </row>
     <row r="195">
       <c r="B195" t="n">
-        <v>1100003</v>
+        <v>1110002</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -3391,11 +3391,11 @@
     </row>
     <row r="196">
       <c r="B196" t="n">
-        <v>1100004</v>
+        <v>1110005</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -3406,11 +3406,11 @@
     </row>
     <row r="197">
       <c r="B197" t="n">
-        <v>1100006</v>
+        <v>1110006</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -3421,11 +3421,11 @@
     </row>
     <row r="198">
       <c r="B198" t="n">
-        <v>1100007</v>
+        <v>1110008</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -3436,26 +3436,26 @@
     </row>
     <row r="199">
       <c r="B199" t="n">
-        <v>1100009</v>
+        <v>103</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="B200" t="n">
-        <v>1100010</v>
+        <v>102</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -3466,11 +3466,11 @@
     </row>
     <row r="201">
       <c r="B201" t="n">
-        <v>1100011</v>
+        <v>1110002</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -3481,11 +3481,11 @@
     </row>
     <row r="202">
       <c r="B202" t="n">
-        <v>1100012</v>
+        <v>1110003</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -3496,11 +3496,11 @@
     </row>
     <row r="203">
       <c r="B203" t="n">
-        <v>97</v>
+        <v>1110004</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -3511,11 +3511,11 @@
     </row>
     <row r="204">
       <c r="B204" t="n">
-        <v>99</v>
+        <v>1110005</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -3526,11 +3526,11 @@
     </row>
     <row r="205">
       <c r="B205" t="n">
-        <v>1100006</v>
+        <v>1110006</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -3541,14 +3541,614 @@
     </row>
     <row r="206">
       <c r="B206" t="n">
-        <v>1100011</v>
+        <v>1110008</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="B207" t="n">
+        <v>104</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="B208" t="n">
+        <v>1110009</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="B209" t="n">
+        <v>1110011</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="B210" t="n">
+        <v>103</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="B211" t="n">
+        <v>104</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="B212" t="n">
+        <v>1110002</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="B213" t="n">
+        <v>1110005</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="B214" t="n">
+        <v>1110006</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="B215" t="n">
+        <v>1110009</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="B216" t="n">
+        <v>1110011</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="B217" t="n">
+        <v>103</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="B218" t="n">
+        <v>104</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="B219" t="n">
+        <v>1110002</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="B220" t="n">
+        <v>1110003</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="B221" t="n">
+        <v>1110004</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="B222" t="n">
+        <v>1110008</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="B223" t="n">
+        <v>1110009</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="B224" t="n">
+        <v>104</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="B225" t="n">
+        <v>1110001</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="B226" t="n">
+        <v>1110005</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="B227" t="n">
+        <v>1110006</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="B228" t="n">
+        <v>1110008</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="B229" t="n">
+        <v>1110011</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="B230" t="n">
+        <v>102</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="B231" t="n">
+        <v>103</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="B232" t="n">
+        <v>104</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="B233" t="n">
+        <v>1110001</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="B234" t="n">
+        <v>1110002</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="B235" t="n">
+        <v>1110003</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="B236" t="n">
+        <v>1110004</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="B237" t="n">
+        <v>1110008</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="B238" t="n">
+        <v>102</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
           <t>Wind</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr">
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="B239" t="n">
+        <v>103</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="B240" t="n">
+        <v>1110001</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="B241" t="n">
+        <v>1110003</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="B242" t="n">
+        <v>1110004</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="B243" t="n">
+        <v>1110005</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="B244" t="n">
+        <v>1110006</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="B245" t="n">
+        <v>1110009</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="B246" t="n">
+        <v>1110011</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>

--- a/config/data/EnemyResistance.xlsx
+++ b/config/data/EnemyResistance.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J246"/>
+  <dimension ref="A1:J286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -706,22 +706,22 @@
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
     </row>
     <row r="19">
       <c r="B19" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
     </row>
     <row r="20">
       <c r="B20" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -766,11 +766,11 @@
     </row>
     <row r="21">
       <c r="B21" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -781,11 +781,11 @@
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -796,11 +796,11 @@
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -811,26 +811,26 @@
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -841,11 +841,11 @@
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -856,11 +856,11 @@
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -871,11 +871,11 @@
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -886,11 +886,11 @@
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -901,11 +901,11 @@
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -916,26 +916,26 @@
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.6</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -946,41 +946,41 @@
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="n">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="n">
-        <v>110</v>
+        <v>980001</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -991,11 +991,11 @@
     </row>
     <row r="36">
       <c r="B36" t="n">
-        <v>110</v>
+        <v>980001</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1006,11 +1006,11 @@
     </row>
     <row r="37">
       <c r="B37" t="n">
-        <v>110</v>
+        <v>980001</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1021,7 +1021,7 @@
     </row>
     <row r="38">
       <c r="B38" t="n">
-        <v>110</v>
+        <v>980001</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
     </row>
     <row r="39">
       <c r="B39" t="n">
-        <v>111</v>
+        <v>990001</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1051,11 +1051,11 @@
     </row>
     <row r="40">
       <c r="B40" t="n">
-        <v>111</v>
+        <v>990001</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1066,11 +1066,11 @@
     </row>
     <row r="41">
       <c r="B41" t="n">
-        <v>111</v>
+        <v>990001</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1081,11 +1081,11 @@
     </row>
     <row r="42">
       <c r="B42" t="n">
-        <v>111</v>
+        <v>990001</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1096,26 +1096,26 @@
     </row>
     <row r="43">
       <c r="B43" t="n">
-        <v>98</v>
+        <v>1000001</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="n">
-        <v>98</v>
+        <v>1000001</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1126,22 +1126,22 @@
     </row>
     <row r="45">
       <c r="B45" t="n">
-        <v>98</v>
+        <v>1000001</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="n">
-        <v>98</v>
+        <v>1000001</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1150,32 +1150,32 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" t="n">
-        <v>980001</v>
+        <v>1010001</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" t="n">
-        <v>980001</v>
+        <v>1010001</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1186,11 +1186,11 @@
     </row>
     <row r="49">
       <c r="B49" t="n">
-        <v>980001</v>
+        <v>1010001</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1201,7 +1201,7 @@
     </row>
     <row r="50">
       <c r="B50" t="n">
-        <v>980001</v>
+        <v>1010001</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
     </row>
     <row r="51">
       <c r="B51" t="n">
-        <v>990001</v>
+        <v>1020001</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1231,26 +1231,26 @@
     </row>
     <row r="52">
       <c r="B52" t="n">
-        <v>990001</v>
+        <v>1020001</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" t="n">
-        <v>990001</v>
+        <v>1020001</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1261,11 +1261,11 @@
     </row>
     <row r="54">
       <c r="B54" t="n">
-        <v>990001</v>
+        <v>1020001</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1276,26 +1276,26 @@
     </row>
     <row r="55">
       <c r="B55" t="n">
-        <v>1000001</v>
+        <v>1030001</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" t="n">
-        <v>1000001</v>
+        <v>1030001</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1306,22 +1306,22 @@
     </row>
     <row r="57">
       <c r="B57" t="n">
-        <v>1000001</v>
+        <v>1030001</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" t="n">
-        <v>1000001</v>
+        <v>1030001</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1330,13 +1330,13 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" t="n">
-        <v>1010001</v>
+        <v>1040001</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1345,32 +1345,32 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" t="n">
-        <v>1010001</v>
+        <v>1040001</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" t="n">
-        <v>1010001</v>
+        <v>1040001</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1381,7 +1381,7 @@
     </row>
     <row r="62">
       <c r="B62" t="n">
-        <v>1010001</v>
+        <v>1040001</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1396,41 +1396,41 @@
     </row>
     <row r="63">
       <c r="B63" t="n">
-        <v>1020001</v>
+        <v>1050001</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" t="n">
-        <v>1020001</v>
+        <v>1050001</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" t="n">
-        <v>1020001</v>
+        <v>1050001</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1441,11 +1441,11 @@
     </row>
     <row r="66">
       <c r="B66" t="n">
-        <v>1020001</v>
+        <v>1050001</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -1456,7 +1456,7 @@
     </row>
     <row r="67">
       <c r="B67" t="n">
-        <v>1030001</v>
+        <v>1060001</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -1465,17 +1465,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="B68" t="n">
-        <v>1030001</v>
+        <v>1060001</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -1486,7 +1486,7 @@
     </row>
     <row r="69">
       <c r="B69" t="n">
-        <v>1030001</v>
+        <v>1060001</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -1495,28 +1495,28 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="B70" t="n">
-        <v>1030001</v>
+        <v>1060001</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="B71" t="n">
-        <v>1040001</v>
+        <v>1070001</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
     </row>
     <row r="72">
       <c r="B72" t="n">
-        <v>1040001</v>
+        <v>1070001</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -1540,32 +1540,32 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="B73" t="n">
-        <v>1040001</v>
+        <v>1070001</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="B74" t="n">
-        <v>1040001</v>
+        <v>1070001</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -1576,7 +1576,7 @@
     </row>
     <row r="75">
       <c r="B75" t="n">
-        <v>1050001</v>
+        <v>1080001</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -1585,13 +1585,13 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="B76" t="n">
-        <v>1050001</v>
+        <v>1080001</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -1606,11 +1606,11 @@
     </row>
     <row r="77">
       <c r="B77" t="n">
-        <v>1050001</v>
+        <v>1080001</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -1621,11 +1621,11 @@
     </row>
     <row r="78">
       <c r="B78" t="n">
-        <v>1050001</v>
+        <v>1080001</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -1636,11 +1636,11 @@
     </row>
     <row r="79">
       <c r="B79" t="n">
-        <v>1060001</v>
+        <v>1090005</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -1651,11 +1651,11 @@
     </row>
     <row r="80">
       <c r="B80" t="n">
-        <v>1060001</v>
+        <v>1090006</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -1666,11 +1666,11 @@
     </row>
     <row r="81">
       <c r="B81" t="n">
-        <v>1060001</v>
+        <v>1090008</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -1681,11 +1681,11 @@
     </row>
     <row r="82">
       <c r="B82" t="n">
-        <v>1060001</v>
+        <v>1090009</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -1696,7 +1696,7 @@
     </row>
     <row r="83">
       <c r="B83" t="n">
-        <v>1070001</v>
+        <v>1090010</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -1711,11 +1711,11 @@
     </row>
     <row r="84">
       <c r="B84" t="n">
-        <v>1070001</v>
+        <v>1090012</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -1726,26 +1726,26 @@
     </row>
     <row r="85">
       <c r="B85" t="n">
-        <v>1070001</v>
+        <v>95</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="B86" t="n">
-        <v>1070001</v>
+        <v>96</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -1756,7 +1756,7 @@
     </row>
     <row r="87">
       <c r="B87" t="n">
-        <v>1080001</v>
+        <v>1090004</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -1771,11 +1771,11 @@
     </row>
     <row r="88">
       <c r="B88" t="n">
-        <v>1080001</v>
+        <v>1090005</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -1786,11 +1786,11 @@
     </row>
     <row r="89">
       <c r="B89" t="n">
-        <v>1080001</v>
+        <v>1090006</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -1801,11 +1801,11 @@
     </row>
     <row r="90">
       <c r="B90" t="n">
-        <v>1080001</v>
+        <v>1090008</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -1816,11 +1816,11 @@
     </row>
     <row r="91">
       <c r="B91" t="n">
-        <v>1090005</v>
+        <v>1090009</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -1831,11 +1831,11 @@
     </row>
     <row r="92">
       <c r="B92" t="n">
-        <v>1090006</v>
+        <v>1090012</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -1846,11 +1846,11 @@
     </row>
     <row r="93">
       <c r="B93" t="n">
-        <v>1090008</v>
+        <v>96</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -1861,11 +1861,11 @@
     </row>
     <row r="94">
       <c r="B94" t="n">
-        <v>1090009</v>
+        <v>1090002</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -1876,11 +1876,11 @@
     </row>
     <row r="95">
       <c r="B95" t="n">
-        <v>1090010</v>
+        <v>1090003</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -1891,11 +1891,11 @@
     </row>
     <row r="96">
       <c r="B96" t="n">
-        <v>1090012</v>
+        <v>1090005</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -1906,11 +1906,11 @@
     </row>
     <row r="97">
       <c r="B97" t="n">
-        <v>95</v>
+        <v>1090011</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -1921,11 +1921,11 @@
     </row>
     <row r="98">
       <c r="B98" t="n">
-        <v>96</v>
+        <v>1090012</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -1936,11 +1936,11 @@
     </row>
     <row r="99">
       <c r="B99" t="n">
-        <v>1090004</v>
+        <v>95</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -1951,41 +1951,41 @@
     </row>
     <row r="100">
       <c r="B100" t="n">
-        <v>1090005</v>
+        <v>1090006</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="B101" t="n">
-        <v>1090006</v>
+        <v>96</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="B102" t="n">
-        <v>1090008</v>
+        <v>1090002</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -1996,11 +1996,11 @@
     </row>
     <row r="103">
       <c r="B103" t="n">
-        <v>1090009</v>
+        <v>1090003</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2011,11 +2011,11 @@
     </row>
     <row r="104">
       <c r="B104" t="n">
-        <v>1090012</v>
+        <v>1090004</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -2026,11 +2026,11 @@
     </row>
     <row r="105">
       <c r="B105" t="n">
-        <v>96</v>
+        <v>1090005</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -2071,11 +2071,11 @@
     </row>
     <row r="108">
       <c r="B108" t="n">
-        <v>1090005</v>
+        <v>1090004</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -2086,11 +2086,11 @@
     </row>
     <row r="109">
       <c r="B109" t="n">
-        <v>1090011</v>
+        <v>1090006</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -2101,11 +2101,11 @@
     </row>
     <row r="110">
       <c r="B110" t="n">
-        <v>1090012</v>
+        <v>1090009</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -2116,11 +2116,11 @@
     </row>
     <row r="111">
       <c r="B111" t="n">
-        <v>95</v>
+        <v>1090010</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -2131,41 +2131,41 @@
     </row>
     <row r="112">
       <c r="B112" t="n">
-        <v>1090006</v>
+        <v>1090011</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="B113" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="B114" t="n">
-        <v>1090002</v>
+        <v>96</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -2176,11 +2176,11 @@
     </row>
     <row r="115">
       <c r="B115" t="n">
-        <v>1090003</v>
+        <v>1090002</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -2191,11 +2191,11 @@
     </row>
     <row r="116">
       <c r="B116" t="n">
-        <v>1090004</v>
+        <v>1090003</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -2206,11 +2206,11 @@
     </row>
     <row r="117">
       <c r="B117" t="n">
-        <v>1090005</v>
+        <v>1090004</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -2221,11 +2221,11 @@
     </row>
     <row r="118">
       <c r="B118" t="n">
-        <v>1090002</v>
+        <v>1090008</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -2236,11 +2236,11 @@
     </row>
     <row r="119">
       <c r="B119" t="n">
-        <v>1090003</v>
+        <v>1090009</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -2251,11 +2251,11 @@
     </row>
     <row r="120">
       <c r="B120" t="n">
-        <v>1090004</v>
+        <v>1090010</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -2266,11 +2266,11 @@
     </row>
     <row r="121">
       <c r="B121" t="n">
-        <v>1090006</v>
+        <v>1090011</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -2281,11 +2281,11 @@
     </row>
     <row r="122">
       <c r="B122" t="n">
-        <v>1090009</v>
+        <v>1090012</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -2296,11 +2296,11 @@
     </row>
     <row r="123">
       <c r="B123" t="n">
-        <v>1090010</v>
+        <v>1090005</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -2311,11 +2311,11 @@
     </row>
     <row r="124">
       <c r="B124" t="n">
-        <v>1090011</v>
+        <v>1090008</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -2326,11 +2326,11 @@
     </row>
     <row r="125">
       <c r="B125" t="n">
-        <v>95</v>
+        <v>1090010</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -2341,11 +2341,11 @@
     </row>
     <row r="126">
       <c r="B126" t="n">
-        <v>96</v>
+        <v>1090011</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -2356,11 +2356,11 @@
     </row>
     <row r="127">
       <c r="B127" t="n">
-        <v>1090002</v>
+        <v>1090012</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -2371,11 +2371,11 @@
     </row>
     <row r="128">
       <c r="B128" t="n">
-        <v>1090003</v>
+        <v>95</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -2386,11 +2386,11 @@
     </row>
     <row r="129">
       <c r="B129" t="n">
-        <v>1090004</v>
+        <v>100</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -2401,11 +2401,11 @@
     </row>
     <row r="130">
       <c r="B130" t="n">
-        <v>1090008</v>
+        <v>1100002</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -2416,11 +2416,11 @@
     </row>
     <row r="131">
       <c r="B131" t="n">
-        <v>1090009</v>
+        <v>1100006</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -2431,11 +2431,11 @@
     </row>
     <row r="132">
       <c r="B132" t="n">
-        <v>1090010</v>
+        <v>1100007</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -2446,11 +2446,11 @@
     </row>
     <row r="133">
       <c r="B133" t="n">
-        <v>1090011</v>
+        <v>1100011</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -2461,11 +2461,11 @@
     </row>
     <row r="134">
       <c r="B134" t="n">
-        <v>1090012</v>
+        <v>1100012</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -2476,11 +2476,11 @@
     </row>
     <row r="135">
       <c r="B135" t="n">
-        <v>1090005</v>
+        <v>97</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -2491,11 +2491,11 @@
     </row>
     <row r="136">
       <c r="B136" t="n">
-        <v>1090008</v>
+        <v>99</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -2506,11 +2506,11 @@
     </row>
     <row r="137">
       <c r="B137" t="n">
-        <v>1090010</v>
+        <v>1100003</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -2521,11 +2521,11 @@
     </row>
     <row r="138">
       <c r="B138" t="n">
-        <v>1090011</v>
+        <v>1100004</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -2536,11 +2536,11 @@
     </row>
     <row r="139">
       <c r="B139" t="n">
-        <v>1090012</v>
+        <v>1100006</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -2551,11 +2551,11 @@
     </row>
     <row r="140">
       <c r="B140" t="n">
-        <v>95</v>
+        <v>1100009</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -2566,11 +2566,11 @@
     </row>
     <row r="141">
       <c r="B141" t="n">
-        <v>100</v>
+        <v>1100010</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -2581,11 +2581,11 @@
     </row>
     <row r="142">
       <c r="B142" t="n">
-        <v>1100002</v>
+        <v>1100011</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -2596,11 +2596,11 @@
     </row>
     <row r="143">
       <c r="B143" t="n">
-        <v>1100006</v>
+        <v>1100012</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -2611,11 +2611,11 @@
     </row>
     <row r="144">
       <c r="B144" t="n">
-        <v>1100007</v>
+        <v>97</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -2626,11 +2626,11 @@
     </row>
     <row r="145">
       <c r="B145" t="n">
-        <v>1100011</v>
+        <v>1100002</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -2641,11 +2641,11 @@
     </row>
     <row r="146">
       <c r="B146" t="n">
-        <v>1100012</v>
+        <v>1100004</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -2656,11 +2656,11 @@
     </row>
     <row r="147">
       <c r="B147" t="n">
-        <v>97</v>
+        <v>1100009</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -2671,11 +2671,11 @@
     </row>
     <row r="148">
       <c r="B148" t="n">
-        <v>99</v>
+        <v>1100010</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -2686,11 +2686,11 @@
     </row>
     <row r="149">
       <c r="B149" t="n">
-        <v>1100003</v>
+        <v>1100012</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -2701,11 +2701,11 @@
     </row>
     <row r="150">
       <c r="B150" t="n">
-        <v>1100004</v>
+        <v>97</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -2716,11 +2716,11 @@
     </row>
     <row r="151">
       <c r="B151" t="n">
-        <v>1100006</v>
+        <v>99</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -2731,11 +2731,11 @@
     </row>
     <row r="152">
       <c r="B152" t="n">
-        <v>1100009</v>
+        <v>100</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -2746,11 +2746,11 @@
     </row>
     <row r="153">
       <c r="B153" t="n">
-        <v>1100010</v>
+        <v>1100002</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -2761,11 +2761,11 @@
     </row>
     <row r="154">
       <c r="B154" t="n">
-        <v>1100011</v>
+        <v>1100003</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -2776,11 +2776,11 @@
     </row>
     <row r="155">
       <c r="B155" t="n">
-        <v>1100012</v>
+        <v>1100007</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -2791,11 +2791,11 @@
     </row>
     <row r="156">
       <c r="B156" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -2806,26 +2806,26 @@
     </row>
     <row r="157">
       <c r="B157" t="n">
-        <v>1100002</v>
+        <v>1100006</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="B158" t="n">
-        <v>1100004</v>
+        <v>100</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -2836,11 +2836,11 @@
     </row>
     <row r="159">
       <c r="B159" t="n">
-        <v>1100009</v>
+        <v>1100002</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -2851,11 +2851,11 @@
     </row>
     <row r="160">
       <c r="B160" t="n">
-        <v>1100010</v>
+        <v>1100003</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -2866,11 +2866,11 @@
     </row>
     <row r="161">
       <c r="B161" t="n">
-        <v>1100012</v>
+        <v>1100004</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -2881,11 +2881,11 @@
     </row>
     <row r="162">
       <c r="B162" t="n">
-        <v>97</v>
+        <v>1100007</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -2896,11 +2896,11 @@
     </row>
     <row r="163">
       <c r="B163" t="n">
-        <v>99</v>
+        <v>1100009</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -2911,11 +2911,11 @@
     </row>
     <row r="164">
       <c r="B164" t="n">
-        <v>100</v>
+        <v>1100010</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -2926,11 +2926,11 @@
     </row>
     <row r="165">
       <c r="B165" t="n">
-        <v>1100002</v>
+        <v>1100011</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -2941,11 +2941,11 @@
     </row>
     <row r="166">
       <c r="B166" t="n">
-        <v>1100003</v>
+        <v>97</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -2956,11 +2956,11 @@
     </row>
     <row r="167">
       <c r="B167" t="n">
-        <v>1100007</v>
+        <v>100</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -2971,11 +2971,11 @@
     </row>
     <row r="168">
       <c r="B168" t="n">
-        <v>99</v>
+        <v>1100002</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -2986,26 +2986,26 @@
     </row>
     <row r="169">
       <c r="B169" t="n">
-        <v>1100006</v>
+        <v>1100003</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="B170" t="n">
-        <v>100</v>
+        <v>1100004</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -3016,11 +3016,11 @@
     </row>
     <row r="171">
       <c r="B171" t="n">
-        <v>1100002</v>
+        <v>1100006</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -3031,11 +3031,11 @@
     </row>
     <row r="172">
       <c r="B172" t="n">
-        <v>1100003</v>
+        <v>1100007</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -3046,11 +3046,11 @@
     </row>
     <row r="173">
       <c r="B173" t="n">
-        <v>1100004</v>
+        <v>1100009</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -3061,11 +3061,11 @@
     </row>
     <row r="174">
       <c r="B174" t="n">
-        <v>1100007</v>
+        <v>1100010</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -3076,11 +3076,11 @@
     </row>
     <row r="175">
       <c r="B175" t="n">
-        <v>1100009</v>
+        <v>1100011</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -3091,11 +3091,11 @@
     </row>
     <row r="176">
       <c r="B176" t="n">
-        <v>1100010</v>
+        <v>1100012</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -3106,11 +3106,11 @@
     </row>
     <row r="177">
       <c r="B177" t="n">
-        <v>1100011</v>
+        <v>97</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -3121,11 +3121,11 @@
     </row>
     <row r="178">
       <c r="B178" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -3136,11 +3136,11 @@
     </row>
     <row r="179">
       <c r="B179" t="n">
-        <v>100</v>
+        <v>1100006</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -3151,11 +3151,11 @@
     </row>
     <row r="180">
       <c r="B180" t="n">
-        <v>1100002</v>
+        <v>1100011</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -3166,11 +3166,11 @@
     </row>
     <row r="181">
       <c r="B181" t="n">
-        <v>1100003</v>
+        <v>102</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -3181,11 +3181,11 @@
     </row>
     <row r="182">
       <c r="B182" t="n">
-        <v>1100004</v>
+        <v>1110001</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -3196,11 +3196,11 @@
     </row>
     <row r="183">
       <c r="B183" t="n">
-        <v>1100006</v>
+        <v>1110002</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -3211,11 +3211,11 @@
     </row>
     <row r="184">
       <c r="B184" t="n">
-        <v>1100007</v>
+        <v>1110005</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -3226,11 +3226,11 @@
     </row>
     <row r="185">
       <c r="B185" t="n">
-        <v>1100009</v>
+        <v>1110006</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -3241,11 +3241,11 @@
     </row>
     <row r="186">
       <c r="B186" t="n">
-        <v>1100010</v>
+        <v>1110008</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -3256,26 +3256,26 @@
     </row>
     <row r="187">
       <c r="B187" t="n">
-        <v>1100011</v>
+        <v>103</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="B188" t="n">
-        <v>1100012</v>
+        <v>102</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -3286,11 +3286,11 @@
     </row>
     <row r="189">
       <c r="B189" t="n">
-        <v>97</v>
+        <v>1110002</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -3301,11 +3301,11 @@
     </row>
     <row r="190">
       <c r="B190" t="n">
-        <v>99</v>
+        <v>1110003</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -3316,11 +3316,11 @@
     </row>
     <row r="191">
       <c r="B191" t="n">
-        <v>1100006</v>
+        <v>1110004</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -3331,11 +3331,11 @@
     </row>
     <row r="192">
       <c r="B192" t="n">
-        <v>1100011</v>
+        <v>1110005</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -3346,11 +3346,11 @@
     </row>
     <row r="193">
       <c r="B193" t="n">
-        <v>102</v>
+        <v>1110006</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -3361,11 +3361,11 @@
     </row>
     <row r="194">
       <c r="B194" t="n">
-        <v>1110001</v>
+        <v>1110008</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -3376,56 +3376,56 @@
     </row>
     <row r="195">
       <c r="B195" t="n">
-        <v>1110002</v>
+        <v>104</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="B196" t="n">
-        <v>1110005</v>
+        <v>1110009</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="B197" t="n">
-        <v>1110006</v>
+        <v>1110011</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="B198" t="n">
-        <v>1110008</v>
+        <v>103</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -3436,26 +3436,26 @@
     </row>
     <row r="199">
       <c r="B199" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="B200" t="n">
-        <v>102</v>
+        <v>1110002</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -3466,11 +3466,11 @@
     </row>
     <row r="201">
       <c r="B201" t="n">
-        <v>1110002</v>
+        <v>1110005</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -3481,11 +3481,11 @@
     </row>
     <row r="202">
       <c r="B202" t="n">
-        <v>1110003</v>
+        <v>1110006</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -3496,11 +3496,11 @@
     </row>
     <row r="203">
       <c r="B203" t="n">
-        <v>1110004</v>
+        <v>1110009</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -3511,11 +3511,11 @@
     </row>
     <row r="204">
       <c r="B204" t="n">
-        <v>1110005</v>
+        <v>1110011</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -3526,11 +3526,11 @@
     </row>
     <row r="205">
       <c r="B205" t="n">
-        <v>1110006</v>
+        <v>103</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -3541,11 +3541,11 @@
     </row>
     <row r="206">
       <c r="B206" t="n">
-        <v>1110008</v>
+        <v>104</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -3556,56 +3556,56 @@
     </row>
     <row r="207">
       <c r="B207" t="n">
-        <v>104</v>
+        <v>1110002</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="B208" t="n">
-        <v>1110009</v>
+        <v>1110003</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="B209" t="n">
-        <v>1110011</v>
+        <v>1110004</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="B210" t="n">
-        <v>103</v>
+        <v>1110008</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -3616,11 +3616,11 @@
     </row>
     <row r="211">
       <c r="B211" t="n">
-        <v>104</v>
+        <v>1110009</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -3631,11 +3631,11 @@
     </row>
     <row r="212">
       <c r="B212" t="n">
-        <v>1110002</v>
+        <v>104</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -3646,11 +3646,11 @@
     </row>
     <row r="213">
       <c r="B213" t="n">
-        <v>1110005</v>
+        <v>1110001</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -3661,11 +3661,11 @@
     </row>
     <row r="214">
       <c r="B214" t="n">
-        <v>1110006</v>
+        <v>1110005</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -3676,11 +3676,11 @@
     </row>
     <row r="215">
       <c r="B215" t="n">
-        <v>1110009</v>
+        <v>1110006</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -3691,11 +3691,11 @@
     </row>
     <row r="216">
       <c r="B216" t="n">
-        <v>1110011</v>
+        <v>1110008</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -3706,11 +3706,11 @@
     </row>
     <row r="217">
       <c r="B217" t="n">
-        <v>103</v>
+        <v>1110011</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -3721,11 +3721,11 @@
     </row>
     <row r="218">
       <c r="B218" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -3736,11 +3736,11 @@
     </row>
     <row r="219">
       <c r="B219" t="n">
-        <v>1110002</v>
+        <v>103</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -3751,11 +3751,11 @@
     </row>
     <row r="220">
       <c r="B220" t="n">
-        <v>1110003</v>
+        <v>104</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -3766,11 +3766,11 @@
     </row>
     <row r="221">
       <c r="B221" t="n">
-        <v>1110004</v>
+        <v>1110001</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -3781,11 +3781,11 @@
     </row>
     <row r="222">
       <c r="B222" t="n">
-        <v>1110008</v>
+        <v>1110002</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -3796,11 +3796,11 @@
     </row>
     <row r="223">
       <c r="B223" t="n">
-        <v>1110009</v>
+        <v>1110003</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -3811,11 +3811,11 @@
     </row>
     <row r="224">
       <c r="B224" t="n">
-        <v>104</v>
+        <v>1110004</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -3826,11 +3826,11 @@
     </row>
     <row r="225">
       <c r="B225" t="n">
-        <v>1110001</v>
+        <v>1110008</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -3841,11 +3841,11 @@
     </row>
     <row r="226">
       <c r="B226" t="n">
-        <v>1110005</v>
+        <v>102</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -3856,11 +3856,11 @@
     </row>
     <row r="227">
       <c r="B227" t="n">
-        <v>1110006</v>
+        <v>103</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -3871,11 +3871,11 @@
     </row>
     <row r="228">
       <c r="B228" t="n">
-        <v>1110008</v>
+        <v>1110001</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -3886,11 +3886,11 @@
     </row>
     <row r="229">
       <c r="B229" t="n">
-        <v>1110011</v>
+        <v>1110003</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -3901,11 +3901,11 @@
     </row>
     <row r="230">
       <c r="B230" t="n">
-        <v>102</v>
+        <v>1110004</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -3916,11 +3916,11 @@
     </row>
     <row r="231">
       <c r="B231" t="n">
-        <v>103</v>
+        <v>1110005</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -3931,11 +3931,11 @@
     </row>
     <row r="232">
       <c r="B232" t="n">
-        <v>104</v>
+        <v>1110006</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -3946,11 +3946,11 @@
     </row>
     <row r="233">
       <c r="B233" t="n">
-        <v>1110001</v>
+        <v>1110009</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -3961,11 +3961,11 @@
     </row>
     <row r="234">
       <c r="B234" t="n">
-        <v>1110002</v>
+        <v>1110011</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -3976,11 +3976,11 @@
     </row>
     <row r="235">
       <c r="B235" t="n">
-        <v>1110003</v>
+        <v>108</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -3991,11 +3991,11 @@
     </row>
     <row r="236">
       <c r="B236" t="n">
-        <v>1110004</v>
+        <v>1120003</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -4006,11 +4006,11 @@
     </row>
     <row r="237">
       <c r="B237" t="n">
-        <v>1110008</v>
+        <v>1120004</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -4021,11 +4021,11 @@
     </row>
     <row r="238">
       <c r="B238" t="n">
-        <v>102</v>
+        <v>1120006</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -4036,11 +4036,11 @@
     </row>
     <row r="239">
       <c r="B239" t="n">
-        <v>103</v>
+        <v>1120011</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -4051,26 +4051,26 @@
     </row>
     <row r="240">
       <c r="B240" t="n">
-        <v>1110001</v>
+        <v>106</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="B241" t="n">
-        <v>1110003</v>
+        <v>1120003</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -4081,11 +4081,11 @@
     </row>
     <row r="242">
       <c r="B242" t="n">
-        <v>1110004</v>
+        <v>1120004</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -4096,11 +4096,11 @@
     </row>
     <row r="243">
       <c r="B243" t="n">
-        <v>1110005</v>
+        <v>1120006</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -4111,11 +4111,11 @@
     </row>
     <row r="244">
       <c r="B244" t="n">
-        <v>1110006</v>
+        <v>1120007</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -4126,11 +4126,11 @@
     </row>
     <row r="245">
       <c r="B245" t="n">
-        <v>1110009</v>
+        <v>1120010</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -4141,16 +4141,616 @@
     </row>
     <row r="246">
       <c r="B246" t="n">
-        <v>1110011</v>
+        <v>107</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="B247" t="n">
+        <v>108</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="B248" t="n">
+        <v>1120001</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="B249" t="n">
+        <v>1120002</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="B250" t="n">
+        <v>1120003</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="B251" t="n">
+        <v>1120004</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="B252" t="n">
+        <v>1120010</v>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="B253" t="n">
+        <v>1120011</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="B254" t="n">
+        <v>1120012</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="B255" t="n">
+        <v>106</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="B256" t="n">
+        <v>107</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="B257" t="n">
+        <v>1120001</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="B258" t="n">
+        <v>1120002</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="B259" t="n">
+        <v>1120003</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="B260" t="n">
+        <v>1120006</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="B261" t="n">
+        <v>1120007</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="B262" t="n">
+        <v>1120010</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="B263" t="n">
+        <v>106</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="B264" t="n">
+        <v>107</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="B265" t="n">
+        <v>108</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="B266" t="n">
+        <v>1120001</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="B267" t="n">
+        <v>1120006</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="B268" t="n">
+        <v>1120010</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="B269" t="n">
+        <v>1120011</v>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="B270" t="n">
+        <v>1120012</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="B271" t="n">
+        <v>106</v>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="B272" t="n">
+        <v>1120001</v>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="B273" t="n">
+        <v>1120002</v>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="B274" t="n">
+        <v>1120007</v>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="B275" t="n">
+        <v>1120011</v>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="B276" t="n">
+        <v>1120012</v>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="B277" t="n">
+        <v>108</v>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
           <t>Wind</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>0.2</t>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="B278" t="n">
+        <v>1120001</v>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="B279" t="n">
+        <v>1120002</v>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="B280" t="n">
+        <v>1120004</v>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="B281" t="n">
+        <v>1120006</v>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="B282" t="n">
+        <v>1120007</v>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="B283" t="n">
+        <v>1120010</v>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="B284" t="n">
+        <v>1120011</v>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="B285" t="n">
+        <v>1120012</v>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="B286" t="n">
+        <v>107</v>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>0.4</t>
         </is>
       </c>
     </row>

--- a/config/data/EnemyResistance.xlsx
+++ b/config/data/EnemyResistance.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J286"/>
+  <dimension ref="A1:J336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4754,6 +4754,756 @@
         </is>
       </c>
     </row>
+    <row r="287">
+      <c r="B287" t="n">
+        <v>1130001</v>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="B288" t="n">
+        <v>1130002</v>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="B289" t="n">
+        <v>1130006</v>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="B290" t="n">
+        <v>1130007</v>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="B291" t="n">
+        <v>1130008</v>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="B292" t="n">
+        <v>1130009</v>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="B293" t="n">
+        <v>1130012</v>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="B294" t="n">
+        <v>1130003</v>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="B295" t="n">
+        <v>1130001</v>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="B296" t="n">
+        <v>1130002</v>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="B297" t="n">
+        <v>1130009</v>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="B298" t="n">
+        <v>1130007</v>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="B299" t="n">
+        <v>1130008</v>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="B300" t="n">
+        <v>1130009</v>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="B301" t="n">
+        <v>1130012</v>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="B302" t="n">
+        <v>1130002</v>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="B303" t="n">
+        <v>1130004</v>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="B304" t="n">
+        <v>1130005</v>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="B305" t="n">
+        <v>1130006</v>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="B306" t="n">
+        <v>1130007</v>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="B307" t="n">
+        <v>1130008</v>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="B308" t="n">
+        <v>1130009</v>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="B309" t="n">
+        <v>1130010</v>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="B310" t="n">
+        <v>1130011</v>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="B311" t="n">
+        <v>1130001</v>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="B312" t="n">
+        <v>1130003</v>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="B313" t="n">
+        <v>1130004</v>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="B314" t="n">
+        <v>1130005</v>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="B315" t="n">
+        <v>1130009</v>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="B316" t="n">
+        <v>1130010</v>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="B317" t="n">
+        <v>1130011</v>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="B318" t="n">
+        <v>1130002</v>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="B319" t="n">
+        <v>1130003</v>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="B320" t="n">
+        <v>1130004</v>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="B321" t="n">
+        <v>1130005</v>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="B322" t="n">
+        <v>1130006</v>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="B323" t="n">
+        <v>1130007</v>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="B324" t="n">
+        <v>1130010</v>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="B325" t="n">
+        <v>1130011</v>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="B326" t="n">
+        <v>1130012</v>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="B327" t="n">
+        <v>1130001</v>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="B328" t="n">
+        <v>1130003</v>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="B329" t="n">
+        <v>1130004</v>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="B330" t="n">
+        <v>1130005</v>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="B331" t="n">
+        <v>1130006</v>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="B332" t="n">
+        <v>1130007</v>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="B333" t="n">
+        <v>1130008</v>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="B334" t="n">
+        <v>1130010</v>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="B335" t="n">
+        <v>1130011</v>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="B336" t="n">
+        <v>1130012</v>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyResistance.xlsx
+++ b/config/data/EnemyResistance.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J336"/>
+  <dimension ref="A1:J382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,7 +781,7 @@
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -811,11 +811,11 @@
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -826,7 +826,7 @@
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -841,26 +841,26 @@
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -871,41 +871,41 @@
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>111</v>
+        <v>980001</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -916,26 +916,26 @@
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -946,41 +946,41 @@
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="n">
-        <v>98</v>
+        <v>990001</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -991,11 +991,11 @@
     </row>
     <row r="36">
       <c r="B36" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1006,11 +1006,11 @@
     </row>
     <row r="37">
       <c r="B37" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1021,11 +1021,11 @@
     </row>
     <row r="38">
       <c r="B38" t="n">
-        <v>980001</v>
+        <v>1000001</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1036,11 +1036,11 @@
     </row>
     <row r="39">
       <c r="B39" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1051,11 +1051,11 @@
     </row>
     <row r="40">
       <c r="B40" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1066,11 +1066,11 @@
     </row>
     <row r="41">
       <c r="B41" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1081,22 +1081,22 @@
     </row>
     <row r="42">
       <c r="B42" t="n">
-        <v>990001</v>
+        <v>1010001</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="n">
-        <v>1000001</v>
+        <v>1010001</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1111,11 +1111,11 @@
     </row>
     <row r="44">
       <c r="B44" t="n">
-        <v>1000001</v>
+        <v>1010001</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1126,11 +1126,11 @@
     </row>
     <row r="45">
       <c r="B45" t="n">
-        <v>1000001</v>
+        <v>1010001</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1141,11 +1141,11 @@
     </row>
     <row r="46">
       <c r="B46" t="n">
-        <v>1000001</v>
+        <v>1020001</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1156,11 +1156,11 @@
     </row>
     <row r="47">
       <c r="B47" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1171,11 +1171,11 @@
     </row>
     <row r="48">
       <c r="B48" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1186,11 +1186,11 @@
     </row>
     <row r="49">
       <c r="B49" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1201,26 +1201,26 @@
     </row>
     <row r="50">
       <c r="B50" t="n">
-        <v>1010001</v>
+        <v>1030001</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.6</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1231,11 +1231,11 @@
     </row>
     <row r="52">
       <c r="B52" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1246,26 +1246,26 @@
     </row>
     <row r="53">
       <c r="B53" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" t="n">
-        <v>1020001</v>
+        <v>1040001</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1276,7 +1276,7 @@
     </row>
     <row r="55">
       <c r="B55" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1285,17 +1285,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1306,26 +1306,26 @@
     </row>
     <row r="57">
       <c r="B57" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" t="n">
-        <v>1030001</v>
+        <v>1050001</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1336,11 +1336,11 @@
     </row>
     <row r="59">
       <c r="B59" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1351,26 +1351,26 @@
     </row>
     <row r="60">
       <c r="B60" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1381,11 +1381,11 @@
     </row>
     <row r="62">
       <c r="B62" t="n">
-        <v>1040001</v>
+        <v>1060001</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1396,26 +1396,26 @@
     </row>
     <row r="63">
       <c r="B63" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1426,11 +1426,11 @@
     </row>
     <row r="65">
       <c r="B65" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1441,11 +1441,11 @@
     </row>
     <row r="66">
       <c r="B66" t="n">
-        <v>1050001</v>
+        <v>1070001</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -1456,7 +1456,7 @@
     </row>
     <row r="67">
       <c r="B67" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
     </row>
     <row r="68">
       <c r="B68" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -1480,17 +1480,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="B69" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -1501,11 +1501,11 @@
     </row>
     <row r="70">
       <c r="B70" t="n">
-        <v>1060001</v>
+        <v>1080001</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -1516,11 +1516,11 @@
     </row>
     <row r="71">
       <c r="B71" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -1531,11 +1531,11 @@
     </row>
     <row r="72">
       <c r="B72" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -1546,26 +1546,26 @@
     </row>
     <row r="73">
       <c r="B73" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="B74" t="n">
-        <v>1070001</v>
+        <v>1090005</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -1576,11 +1576,11 @@
     </row>
     <row r="75">
       <c r="B75" t="n">
-        <v>1080001</v>
+        <v>1090006</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -1591,11 +1591,11 @@
     </row>
     <row r="76">
       <c r="B76" t="n">
-        <v>1080001</v>
+        <v>1090008</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -1606,11 +1606,11 @@
     </row>
     <row r="77">
       <c r="B77" t="n">
-        <v>1080001</v>
+        <v>1090009</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -1621,11 +1621,11 @@
     </row>
     <row r="78">
       <c r="B78" t="n">
-        <v>1080001</v>
+        <v>1090010</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -1636,7 +1636,7 @@
     </row>
     <row r="79">
       <c r="B79" t="n">
-        <v>1090005</v>
+        <v>1090012</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
     </row>
     <row r="80">
       <c r="B80" t="n">
-        <v>1090006</v>
+        <v>95</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
     </row>
     <row r="81">
       <c r="B81" t="n">
-        <v>1090008</v>
+        <v>96</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -1681,11 +1681,11 @@
     </row>
     <row r="82">
       <c r="B82" t="n">
-        <v>1090009</v>
+        <v>1090004</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -1696,11 +1696,11 @@
     </row>
     <row r="83">
       <c r="B83" t="n">
-        <v>1090010</v>
+        <v>1090005</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -1711,11 +1711,11 @@
     </row>
     <row r="84">
       <c r="B84" t="n">
-        <v>1090012</v>
+        <v>1090006</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -1726,11 +1726,11 @@
     </row>
     <row r="85">
       <c r="B85" t="n">
-        <v>95</v>
+        <v>1090008</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -1741,11 +1741,11 @@
     </row>
     <row r="86">
       <c r="B86" t="n">
-        <v>96</v>
+        <v>1090009</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -1756,7 +1756,7 @@
     </row>
     <row r="87">
       <c r="B87" t="n">
-        <v>1090004</v>
+        <v>1090012</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
     </row>
     <row r="88">
       <c r="B88" t="n">
-        <v>1090005</v>
+        <v>96</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -1786,11 +1786,11 @@
     </row>
     <row r="89">
       <c r="B89" t="n">
-        <v>1090006</v>
+        <v>1090002</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -1801,11 +1801,11 @@
     </row>
     <row r="90">
       <c r="B90" t="n">
-        <v>1090008</v>
+        <v>1090003</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -1816,11 +1816,11 @@
     </row>
     <row r="91">
       <c r="B91" t="n">
-        <v>1090009</v>
+        <v>1090005</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -1831,11 +1831,11 @@
     </row>
     <row r="92">
       <c r="B92" t="n">
-        <v>1090012</v>
+        <v>1090011</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -1846,11 +1846,11 @@
     </row>
     <row r="93">
       <c r="B93" t="n">
-        <v>96</v>
+        <v>1090012</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -1861,7 +1861,7 @@
     </row>
     <row r="94">
       <c r="B94" t="n">
-        <v>1090002</v>
+        <v>95</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
     </row>
     <row r="95">
       <c r="B95" t="n">
-        <v>1090003</v>
+        <v>1090006</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -1885,13 +1885,13 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="B96" t="n">
-        <v>1090005</v>
+        <v>96</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -1900,17 +1900,17 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="B97" t="n">
-        <v>1090011</v>
+        <v>1090002</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -1921,11 +1921,11 @@
     </row>
     <row r="98">
       <c r="B98" t="n">
-        <v>1090012</v>
+        <v>1090003</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -1936,11 +1936,11 @@
     </row>
     <row r="99">
       <c r="B99" t="n">
-        <v>95</v>
+        <v>1090004</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -1951,41 +1951,41 @@
     </row>
     <row r="100">
       <c r="B100" t="n">
-        <v>1090006</v>
+        <v>1090005</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="B101" t="n">
-        <v>96</v>
+        <v>1090002</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="B102" t="n">
-        <v>1090002</v>
+        <v>1090003</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -1996,11 +1996,11 @@
     </row>
     <row r="103">
       <c r="B103" t="n">
-        <v>1090003</v>
+        <v>1090004</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2011,11 +2011,11 @@
     </row>
     <row r="104">
       <c r="B104" t="n">
-        <v>1090004</v>
+        <v>1090006</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -2026,11 +2026,11 @@
     </row>
     <row r="105">
       <c r="B105" t="n">
-        <v>1090005</v>
+        <v>1090009</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -2041,7 +2041,7 @@
     </row>
     <row r="106">
       <c r="B106" t="n">
-        <v>1090002</v>
+        <v>1090010</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
     </row>
     <row r="107">
       <c r="B107" t="n">
-        <v>1090003</v>
+        <v>1090011</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
     </row>
     <row r="108">
       <c r="B108" t="n">
-        <v>1090004</v>
+        <v>95</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
     </row>
     <row r="109">
       <c r="B109" t="n">
-        <v>1090006</v>
+        <v>96</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -2101,11 +2101,11 @@
     </row>
     <row r="110">
       <c r="B110" t="n">
-        <v>1090009</v>
+        <v>1090002</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -2116,11 +2116,11 @@
     </row>
     <row r="111">
       <c r="B111" t="n">
-        <v>1090010</v>
+        <v>1090003</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -2131,11 +2131,11 @@
     </row>
     <row r="112">
       <c r="B112" t="n">
-        <v>1090011</v>
+        <v>1090004</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -2146,11 +2146,11 @@
     </row>
     <row r="113">
       <c r="B113" t="n">
-        <v>95</v>
+        <v>1090008</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -2161,11 +2161,11 @@
     </row>
     <row r="114">
       <c r="B114" t="n">
-        <v>96</v>
+        <v>1090009</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -2176,7 +2176,7 @@
     </row>
     <row r="115">
       <c r="B115" t="n">
-        <v>1090002</v>
+        <v>1090010</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
     </row>
     <row r="116">
       <c r="B116" t="n">
-        <v>1090003</v>
+        <v>1090011</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
     </row>
     <row r="117">
       <c r="B117" t="n">
-        <v>1090004</v>
+        <v>1090012</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -2221,11 +2221,11 @@
     </row>
     <row r="118">
       <c r="B118" t="n">
-        <v>1090008</v>
+        <v>1090005</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -2236,11 +2236,11 @@
     </row>
     <row r="119">
       <c r="B119" t="n">
-        <v>1090009</v>
+        <v>1090008</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -2296,7 +2296,7 @@
     </row>
     <row r="123">
       <c r="B123" t="n">
-        <v>1090005</v>
+        <v>95</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -2311,11 +2311,11 @@
     </row>
     <row r="124">
       <c r="B124" t="n">
-        <v>1090008</v>
+        <v>100</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -2326,11 +2326,11 @@
     </row>
     <row r="125">
       <c r="B125" t="n">
-        <v>1090010</v>
+        <v>1100002</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -2341,11 +2341,11 @@
     </row>
     <row r="126">
       <c r="B126" t="n">
-        <v>1090011</v>
+        <v>1100006</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -2356,11 +2356,11 @@
     </row>
     <row r="127">
       <c r="B127" t="n">
-        <v>1090012</v>
+        <v>1100007</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -2371,11 +2371,11 @@
     </row>
     <row r="128">
       <c r="B128" t="n">
-        <v>95</v>
+        <v>1100011</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -2386,7 +2386,7 @@
     </row>
     <row r="129">
       <c r="B129" t="n">
-        <v>100</v>
+        <v>1100012</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
     </row>
     <row r="130">
       <c r="B130" t="n">
-        <v>1100002</v>
+        <v>97</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
     </row>
     <row r="131">
       <c r="B131" t="n">
-        <v>1100006</v>
+        <v>99</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -2431,11 +2431,11 @@
     </row>
     <row r="132">
       <c r="B132" t="n">
-        <v>1100007</v>
+        <v>1100003</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -2446,11 +2446,11 @@
     </row>
     <row r="133">
       <c r="B133" t="n">
-        <v>1100011</v>
+        <v>1100004</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -2461,11 +2461,11 @@
     </row>
     <row r="134">
       <c r="B134" t="n">
-        <v>1100012</v>
+        <v>1100006</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -2476,11 +2476,11 @@
     </row>
     <row r="135">
       <c r="B135" t="n">
-        <v>97</v>
+        <v>1100009</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -2491,11 +2491,11 @@
     </row>
     <row r="136">
       <c r="B136" t="n">
-        <v>99</v>
+        <v>1100010</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -2506,7 +2506,7 @@
     </row>
     <row r="137">
       <c r="B137" t="n">
-        <v>1100003</v>
+        <v>1100011</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
     </row>
     <row r="138">
       <c r="B138" t="n">
-        <v>1100004</v>
+        <v>1100012</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
     </row>
     <row r="139">
       <c r="B139" t="n">
-        <v>1100006</v>
+        <v>97</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -2551,11 +2551,11 @@
     </row>
     <row r="140">
       <c r="B140" t="n">
-        <v>1100009</v>
+        <v>1100002</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -2566,11 +2566,11 @@
     </row>
     <row r="141">
       <c r="B141" t="n">
-        <v>1100010</v>
+        <v>1100004</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -2581,11 +2581,11 @@
     </row>
     <row r="142">
       <c r="B142" t="n">
-        <v>1100011</v>
+        <v>1100009</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -2596,11 +2596,11 @@
     </row>
     <row r="143">
       <c r="B143" t="n">
-        <v>1100012</v>
+        <v>1100010</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -2611,11 +2611,11 @@
     </row>
     <row r="144">
       <c r="B144" t="n">
-        <v>97</v>
+        <v>1100012</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -2626,7 +2626,7 @@
     </row>
     <row r="145">
       <c r="B145" t="n">
-        <v>1100002</v>
+        <v>97</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
     </row>
     <row r="146">
       <c r="B146" t="n">
-        <v>1100004</v>
+        <v>99</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -2656,11 +2656,11 @@
     </row>
     <row r="147">
       <c r="B147" t="n">
-        <v>1100009</v>
+        <v>100</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -2671,11 +2671,11 @@
     </row>
     <row r="148">
       <c r="B148" t="n">
-        <v>1100010</v>
+        <v>1100002</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -2686,11 +2686,11 @@
     </row>
     <row r="149">
       <c r="B149" t="n">
-        <v>1100012</v>
+        <v>1100003</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -2701,11 +2701,11 @@
     </row>
     <row r="150">
       <c r="B150" t="n">
-        <v>97</v>
+        <v>1100007</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -2731,7 +2731,7 @@
     </row>
     <row r="152">
       <c r="B152" t="n">
-        <v>100</v>
+        <v>1100006</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -2740,17 +2740,17 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="B153" t="n">
-        <v>1100002</v>
+        <v>100</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -2761,11 +2761,11 @@
     </row>
     <row r="154">
       <c r="B154" t="n">
-        <v>1100003</v>
+        <v>1100002</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -2776,11 +2776,11 @@
     </row>
     <row r="155">
       <c r="B155" t="n">
-        <v>1100007</v>
+        <v>1100003</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -2791,11 +2791,11 @@
     </row>
     <row r="156">
       <c r="B156" t="n">
-        <v>99</v>
+        <v>1100004</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -2806,22 +2806,22 @@
     </row>
     <row r="157">
       <c r="B157" t="n">
-        <v>1100006</v>
+        <v>1100007</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="B158" t="n">
-        <v>100</v>
+        <v>1100009</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
     </row>
     <row r="159">
       <c r="B159" t="n">
-        <v>1100002</v>
+        <v>1100010</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
     </row>
     <row r="160">
       <c r="B160" t="n">
-        <v>1100003</v>
+        <v>1100011</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
     </row>
     <row r="161">
       <c r="B161" t="n">
-        <v>1100004</v>
+        <v>97</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -2881,11 +2881,11 @@
     </row>
     <row r="162">
       <c r="B162" t="n">
-        <v>1100007</v>
+        <v>100</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -2896,11 +2896,11 @@
     </row>
     <row r="163">
       <c r="B163" t="n">
-        <v>1100009</v>
+        <v>1100002</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -2911,11 +2911,11 @@
     </row>
     <row r="164">
       <c r="B164" t="n">
-        <v>1100010</v>
+        <v>1100003</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -2926,11 +2926,11 @@
     </row>
     <row r="165">
       <c r="B165" t="n">
-        <v>1100011</v>
+        <v>1100004</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -2941,11 +2941,11 @@
     </row>
     <row r="166">
       <c r="B166" t="n">
-        <v>97</v>
+        <v>1100006</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -2956,7 +2956,7 @@
     </row>
     <row r="167">
       <c r="B167" t="n">
-        <v>100</v>
+        <v>1100007</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
     </row>
     <row r="168">
       <c r="B168" t="n">
-        <v>1100002</v>
+        <v>1100009</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
     </row>
     <row r="169">
       <c r="B169" t="n">
-        <v>1100003</v>
+        <v>1100010</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
     </row>
     <row r="170">
       <c r="B170" t="n">
-        <v>1100004</v>
+        <v>1100011</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
     </row>
     <row r="171">
       <c r="B171" t="n">
-        <v>1100006</v>
+        <v>1100012</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
     </row>
     <row r="172">
       <c r="B172" t="n">
-        <v>1100007</v>
+        <v>97</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
     </row>
     <row r="173">
       <c r="B173" t="n">
-        <v>1100009</v>
+        <v>99</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -3061,11 +3061,11 @@
     </row>
     <row r="174">
       <c r="B174" t="n">
-        <v>1100010</v>
+        <v>1100006</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -3091,11 +3091,11 @@
     </row>
     <row r="176">
       <c r="B176" t="n">
-        <v>1100012</v>
+        <v>102</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -3106,11 +3106,11 @@
     </row>
     <row r="177">
       <c r="B177" t="n">
-        <v>97</v>
+        <v>1110001</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -3121,11 +3121,11 @@
     </row>
     <row r="178">
       <c r="B178" t="n">
-        <v>99</v>
+        <v>1110002</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -3136,11 +3136,11 @@
     </row>
     <row r="179">
       <c r="B179" t="n">
-        <v>1100006</v>
+        <v>1110005</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -3151,11 +3151,11 @@
     </row>
     <row r="180">
       <c r="B180" t="n">
-        <v>1100011</v>
+        <v>1110006</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -3166,7 +3166,7 @@
     </row>
     <row r="181">
       <c r="B181" t="n">
-        <v>102</v>
+        <v>1110008</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
     </row>
     <row r="182">
       <c r="B182" t="n">
-        <v>1110001</v>
+        <v>103</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -3190,17 +3190,17 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="B183" t="n">
-        <v>1110002</v>
+        <v>102</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -3211,11 +3211,11 @@
     </row>
     <row r="184">
       <c r="B184" t="n">
-        <v>1110005</v>
+        <v>1110002</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -3226,11 +3226,11 @@
     </row>
     <row r="185">
       <c r="B185" t="n">
-        <v>1110006</v>
+        <v>1110003</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -3241,11 +3241,11 @@
     </row>
     <row r="186">
       <c r="B186" t="n">
-        <v>1110008</v>
+        <v>1110004</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -3256,22 +3256,22 @@
     </row>
     <row r="187">
       <c r="B187" t="n">
-        <v>103</v>
+        <v>1110005</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="B188" t="n">
-        <v>102</v>
+        <v>1110006</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="189">
       <c r="B189" t="n">
-        <v>1110002</v>
+        <v>1110008</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
     </row>
     <row r="190">
       <c r="B190" t="n">
-        <v>1110003</v>
+        <v>104</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -3310,13 +3310,13 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="B191" t="n">
-        <v>1110004</v>
+        <v>1110009</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -3325,13 +3325,13 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="B192" t="n">
-        <v>1110005</v>
+        <v>1110011</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -3340,17 +3340,17 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="B193" t="n">
-        <v>1110006</v>
+        <v>103</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -3361,11 +3361,11 @@
     </row>
     <row r="194">
       <c r="B194" t="n">
-        <v>1110008</v>
+        <v>104</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -3376,52 +3376,52 @@
     </row>
     <row r="195">
       <c r="B195" t="n">
-        <v>104</v>
+        <v>1110002</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="B196" t="n">
-        <v>1110009</v>
+        <v>1110005</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="B197" t="n">
-        <v>1110011</v>
+        <v>1110006</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="B198" t="n">
-        <v>103</v>
+        <v>1110009</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
     </row>
     <row r="199">
       <c r="B199" t="n">
-        <v>104</v>
+        <v>1110011</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -3451,11 +3451,11 @@
     </row>
     <row r="200">
       <c r="B200" t="n">
-        <v>1110002</v>
+        <v>103</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -3466,11 +3466,11 @@
     </row>
     <row r="201">
       <c r="B201" t="n">
-        <v>1110005</v>
+        <v>104</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -3481,11 +3481,11 @@
     </row>
     <row r="202">
       <c r="B202" t="n">
-        <v>1110006</v>
+        <v>1110002</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -3496,11 +3496,11 @@
     </row>
     <row r="203">
       <c r="B203" t="n">
-        <v>1110009</v>
+        <v>1110003</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -3511,11 +3511,11 @@
     </row>
     <row r="204">
       <c r="B204" t="n">
-        <v>1110011</v>
+        <v>1110004</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -3526,7 +3526,7 @@
     </row>
     <row r="205">
       <c r="B205" t="n">
-        <v>103</v>
+        <v>1110008</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
     </row>
     <row r="206">
       <c r="B206" t="n">
-        <v>104</v>
+        <v>1110009</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -3556,11 +3556,11 @@
     </row>
     <row r="207">
       <c r="B207" t="n">
-        <v>1110002</v>
+        <v>104</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -3571,11 +3571,11 @@
     </row>
     <row r="208">
       <c r="B208" t="n">
-        <v>1110003</v>
+        <v>1110001</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -3586,11 +3586,11 @@
     </row>
     <row r="209">
       <c r="B209" t="n">
-        <v>1110004</v>
+        <v>1110005</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -3601,11 +3601,11 @@
     </row>
     <row r="210">
       <c r="B210" t="n">
-        <v>1110008</v>
+        <v>1110006</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -3616,11 +3616,11 @@
     </row>
     <row r="211">
       <c r="B211" t="n">
-        <v>1110009</v>
+        <v>1110008</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -3631,7 +3631,7 @@
     </row>
     <row r="212">
       <c r="B212" t="n">
-        <v>104</v>
+        <v>1110011</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -3646,11 +3646,11 @@
     </row>
     <row r="213">
       <c r="B213" t="n">
-        <v>1110001</v>
+        <v>102</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -3661,11 +3661,11 @@
     </row>
     <row r="214">
       <c r="B214" t="n">
-        <v>1110005</v>
+        <v>103</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -3676,11 +3676,11 @@
     </row>
     <row r="215">
       <c r="B215" t="n">
-        <v>1110006</v>
+        <v>104</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -3691,11 +3691,11 @@
     </row>
     <row r="216">
       <c r="B216" t="n">
-        <v>1110008</v>
+        <v>1110001</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -3706,11 +3706,11 @@
     </row>
     <row r="217">
       <c r="B217" t="n">
-        <v>1110011</v>
+        <v>1110002</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -3721,7 +3721,7 @@
     </row>
     <row r="218">
       <c r="B218" t="n">
-        <v>102</v>
+        <v>1110003</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
     </row>
     <row r="219">
       <c r="B219" t="n">
-        <v>103</v>
+        <v>1110004</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
     </row>
     <row r="220">
       <c r="B220" t="n">
-        <v>104</v>
+        <v>1110008</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -3766,11 +3766,11 @@
     </row>
     <row r="221">
       <c r="B221" t="n">
-        <v>1110001</v>
+        <v>102</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -3781,11 +3781,11 @@
     </row>
     <row r="222">
       <c r="B222" t="n">
-        <v>1110002</v>
+        <v>103</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -3796,11 +3796,11 @@
     </row>
     <row r="223">
       <c r="B223" t="n">
-        <v>1110003</v>
+        <v>1110001</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -3811,11 +3811,11 @@
     </row>
     <row r="224">
       <c r="B224" t="n">
-        <v>1110004</v>
+        <v>1110003</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -3826,11 +3826,11 @@
     </row>
     <row r="225">
       <c r="B225" t="n">
-        <v>1110008</v>
+        <v>1110004</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -3841,7 +3841,7 @@
     </row>
     <row r="226">
       <c r="B226" t="n">
-        <v>102</v>
+        <v>1110005</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
     </row>
     <row r="227">
       <c r="B227" t="n">
-        <v>103</v>
+        <v>1110006</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
     </row>
     <row r="228">
       <c r="B228" t="n">
-        <v>1110001</v>
+        <v>1110009</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
     </row>
     <row r="229">
       <c r="B229" t="n">
-        <v>1110003</v>
+        <v>1110011</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -3901,11 +3901,11 @@
     </row>
     <row r="230">
       <c r="B230" t="n">
-        <v>1110004</v>
+        <v>108</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -3916,11 +3916,11 @@
     </row>
     <row r="231">
       <c r="B231" t="n">
-        <v>1110005</v>
+        <v>1120003</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -3931,11 +3931,11 @@
     </row>
     <row r="232">
       <c r="B232" t="n">
-        <v>1110006</v>
+        <v>1120004</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -3946,11 +3946,11 @@
     </row>
     <row r="233">
       <c r="B233" t="n">
-        <v>1110009</v>
+        <v>1120006</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -3961,11 +3961,11 @@
     </row>
     <row r="234">
       <c r="B234" t="n">
-        <v>1110011</v>
+        <v>1120011</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -3976,7 +3976,7 @@
     </row>
     <row r="235">
       <c r="B235" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
@@ -3995,7 +3995,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -4036,11 +4036,11 @@
     </row>
     <row r="239">
       <c r="B239" t="n">
-        <v>1120011</v>
+        <v>1120007</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -4051,26 +4051,26 @@
     </row>
     <row r="240">
       <c r="B240" t="n">
-        <v>106</v>
+        <v>1120010</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="B241" t="n">
-        <v>1120003</v>
+        <v>107</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -4081,11 +4081,11 @@
     </row>
     <row r="242">
       <c r="B242" t="n">
-        <v>1120004</v>
+        <v>108</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -4096,11 +4096,11 @@
     </row>
     <row r="243">
       <c r="B243" t="n">
-        <v>1120006</v>
+        <v>1120001</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -4111,11 +4111,11 @@
     </row>
     <row r="244">
       <c r="B244" t="n">
-        <v>1120007</v>
+        <v>1120002</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -4126,11 +4126,11 @@
     </row>
     <row r="245">
       <c r="B245" t="n">
-        <v>1120010</v>
+        <v>1120003</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -4141,7 +4141,7 @@
     </row>
     <row r="246">
       <c r="B246" t="n">
-        <v>107</v>
+        <v>1120004</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
     </row>
     <row r="247">
       <c r="B247" t="n">
-        <v>108</v>
+        <v>1120010</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
     </row>
     <row r="248">
       <c r="B248" t="n">
-        <v>1120001</v>
+        <v>1120011</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
     </row>
     <row r="249">
       <c r="B249" t="n">
-        <v>1120002</v>
+        <v>1120012</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -4201,11 +4201,11 @@
     </row>
     <row r="250">
       <c r="B250" t="n">
-        <v>1120003</v>
+        <v>106</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -4216,11 +4216,11 @@
     </row>
     <row r="251">
       <c r="B251" t="n">
-        <v>1120004</v>
+        <v>107</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -4231,11 +4231,11 @@
     </row>
     <row r="252">
       <c r="B252" t="n">
-        <v>1120010</v>
+        <v>1120001</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -4246,11 +4246,11 @@
     </row>
     <row r="253">
       <c r="B253" t="n">
-        <v>1120011</v>
+        <v>1120002</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -4261,11 +4261,11 @@
     </row>
     <row r="254">
       <c r="B254" t="n">
-        <v>1120012</v>
+        <v>1120003</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -4276,7 +4276,7 @@
     </row>
     <row r="255">
       <c r="B255" t="n">
-        <v>106</v>
+        <v>1120006</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
     </row>
     <row r="256">
       <c r="B256" t="n">
-        <v>107</v>
+        <v>1120007</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
     </row>
     <row r="257">
       <c r="B257" t="n">
-        <v>1120001</v>
+        <v>1120010</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -4321,11 +4321,11 @@
     </row>
     <row r="258">
       <c r="B258" t="n">
-        <v>1120002</v>
+        <v>106</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -4336,11 +4336,11 @@
     </row>
     <row r="259">
       <c r="B259" t="n">
-        <v>1120003</v>
+        <v>107</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -4351,11 +4351,11 @@
     </row>
     <row r="260">
       <c r="B260" t="n">
-        <v>1120006</v>
+        <v>108</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -4366,11 +4366,11 @@
     </row>
     <row r="261">
       <c r="B261" t="n">
-        <v>1120007</v>
+        <v>1120001</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -4381,11 +4381,11 @@
     </row>
     <row r="262">
       <c r="B262" t="n">
-        <v>1120010</v>
+        <v>1120006</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -4396,7 +4396,7 @@
     </row>
     <row r="263">
       <c r="B263" t="n">
-        <v>106</v>
+        <v>1120010</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
     </row>
     <row r="264">
       <c r="B264" t="n">
-        <v>107</v>
+        <v>1120011</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
     </row>
     <row r="265">
       <c r="B265" t="n">
-        <v>108</v>
+        <v>1120012</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -4441,11 +4441,11 @@
     </row>
     <row r="266">
       <c r="B266" t="n">
-        <v>1120001</v>
+        <v>106</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -4456,11 +4456,11 @@
     </row>
     <row r="267">
       <c r="B267" t="n">
-        <v>1120006</v>
+        <v>1120001</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -4471,11 +4471,11 @@
     </row>
     <row r="268">
       <c r="B268" t="n">
-        <v>1120010</v>
+        <v>1120002</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -4486,11 +4486,11 @@
     </row>
     <row r="269">
       <c r="B269" t="n">
-        <v>1120011</v>
+        <v>1120007</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -4501,11 +4501,11 @@
     </row>
     <row r="270">
       <c r="B270" t="n">
-        <v>1120012</v>
+        <v>1120011</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -4516,7 +4516,7 @@
     </row>
     <row r="271">
       <c r="B271" t="n">
-        <v>106</v>
+        <v>1120012</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -4531,11 +4531,11 @@
     </row>
     <row r="272">
       <c r="B272" t="n">
-        <v>1120001</v>
+        <v>108</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -4546,11 +4546,11 @@
     </row>
     <row r="273">
       <c r="B273" t="n">
-        <v>1120002</v>
+        <v>1120001</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -4561,11 +4561,11 @@
     </row>
     <row r="274">
       <c r="B274" t="n">
-        <v>1120007</v>
+        <v>1120002</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -4576,11 +4576,11 @@
     </row>
     <row r="275">
       <c r="B275" t="n">
-        <v>1120011</v>
+        <v>1120004</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -4591,11 +4591,11 @@
     </row>
     <row r="276">
       <c r="B276" t="n">
-        <v>1120012</v>
+        <v>1120006</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -4606,7 +4606,7 @@
     </row>
     <row r="277">
       <c r="B277" t="n">
-        <v>108</v>
+        <v>1120007</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
     </row>
     <row r="278">
       <c r="B278" t="n">
-        <v>1120001</v>
+        <v>1120010</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
     </row>
     <row r="279">
       <c r="B279" t="n">
-        <v>1120002</v>
+        <v>1120011</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
     </row>
     <row r="280">
       <c r="B280" t="n">
-        <v>1120004</v>
+        <v>1120012</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
     </row>
     <row r="281">
       <c r="B281" t="n">
-        <v>1120006</v>
+        <v>107</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -4675,17 +4675,17 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="B282" t="n">
-        <v>1120007</v>
+        <v>1130001</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -4696,11 +4696,11 @@
     </row>
     <row r="283">
       <c r="B283" t="n">
-        <v>1120010</v>
+        <v>1130002</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -4711,11 +4711,11 @@
     </row>
     <row r="284">
       <c r="B284" t="n">
-        <v>1120011</v>
+        <v>1130006</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -4726,11 +4726,11 @@
     </row>
     <row r="285">
       <c r="B285" t="n">
-        <v>1120012</v>
+        <v>1130007</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -4741,22 +4741,22 @@
     </row>
     <row r="286">
       <c r="B286" t="n">
-        <v>107</v>
+        <v>1130008</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="B287" t="n">
-        <v>1130001</v>
+        <v>1130009</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
     </row>
     <row r="288">
       <c r="B288" t="n">
-        <v>1130002</v>
+        <v>1130012</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
     </row>
     <row r="289">
       <c r="B289" t="n">
-        <v>1130006</v>
+        <v>1130003</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
@@ -4795,17 +4795,17 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="B290" t="n">
-        <v>1130007</v>
+        <v>1130001</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -4816,11 +4816,11 @@
     </row>
     <row r="291">
       <c r="B291" t="n">
-        <v>1130008</v>
+        <v>1130002</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -4835,7 +4835,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -4846,11 +4846,11 @@
     </row>
     <row r="293">
       <c r="B293" t="n">
-        <v>1130012</v>
+        <v>1130007</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -4861,26 +4861,26 @@
     </row>
     <row r="294">
       <c r="B294" t="n">
-        <v>1130003</v>
+        <v>1130008</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="B295" t="n">
-        <v>1130001</v>
+        <v>1130009</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -4891,11 +4891,11 @@
     </row>
     <row r="296">
       <c r="B296" t="n">
-        <v>1130002</v>
+        <v>1130012</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -4906,11 +4906,11 @@
     </row>
     <row r="297">
       <c r="B297" t="n">
-        <v>1130009</v>
+        <v>1130002</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -4921,11 +4921,11 @@
     </row>
     <row r="298">
       <c r="B298" t="n">
-        <v>1130007</v>
+        <v>1130004</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -4936,11 +4936,11 @@
     </row>
     <row r="299">
       <c r="B299" t="n">
-        <v>1130008</v>
+        <v>1130005</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -4951,11 +4951,11 @@
     </row>
     <row r="300">
       <c r="B300" t="n">
-        <v>1130009</v>
+        <v>1130006</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -4966,11 +4966,11 @@
     </row>
     <row r="301">
       <c r="B301" t="n">
-        <v>1130012</v>
+        <v>1130007</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -4981,7 +4981,7 @@
     </row>
     <row r="302">
       <c r="B302" t="n">
-        <v>1130002</v>
+        <v>1130008</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
     </row>
     <row r="303">
       <c r="B303" t="n">
-        <v>1130004</v>
+        <v>1130009</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
     </row>
     <row r="304">
       <c r="B304" t="n">
-        <v>1130005</v>
+        <v>1130010</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
     </row>
     <row r="305">
       <c r="B305" t="n">
-        <v>1130006</v>
+        <v>1130011</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -5041,11 +5041,11 @@
     </row>
     <row r="306">
       <c r="B306" t="n">
-        <v>1130007</v>
+        <v>1130001</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -5056,11 +5056,11 @@
     </row>
     <row r="307">
       <c r="B307" t="n">
-        <v>1130008</v>
+        <v>1130003</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -5071,11 +5071,11 @@
     </row>
     <row r="308">
       <c r="B308" t="n">
-        <v>1130009</v>
+        <v>1130004</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -5086,11 +5086,11 @@
     </row>
     <row r="309">
       <c r="B309" t="n">
-        <v>1130010</v>
+        <v>1130005</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -5101,11 +5101,11 @@
     </row>
     <row r="310">
       <c r="B310" t="n">
-        <v>1130011</v>
+        <v>1130009</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -5116,7 +5116,7 @@
     </row>
     <row r="311">
       <c r="B311" t="n">
-        <v>1130001</v>
+        <v>1130010</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
     </row>
     <row r="312">
       <c r="B312" t="n">
-        <v>1130003</v>
+        <v>1130011</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -5146,11 +5146,11 @@
     </row>
     <row r="313">
       <c r="B313" t="n">
-        <v>1130004</v>
+        <v>1130002</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -5161,11 +5161,11 @@
     </row>
     <row r="314">
       <c r="B314" t="n">
-        <v>1130005</v>
+        <v>1130003</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -5176,11 +5176,11 @@
     </row>
     <row r="315">
       <c r="B315" t="n">
-        <v>1130009</v>
+        <v>1130004</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -5191,11 +5191,11 @@
     </row>
     <row r="316">
       <c r="B316" t="n">
-        <v>1130010</v>
+        <v>1130005</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -5206,11 +5206,11 @@
     </row>
     <row r="317">
       <c r="B317" t="n">
-        <v>1130011</v>
+        <v>1130006</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -5221,7 +5221,7 @@
     </row>
     <row r="318">
       <c r="B318" t="n">
-        <v>1130002</v>
+        <v>1130007</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
     </row>
     <row r="319">
       <c r="B319" t="n">
-        <v>1130003</v>
+        <v>1130010</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
     </row>
     <row r="320">
       <c r="B320" t="n">
-        <v>1130004</v>
+        <v>1130011</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
     </row>
     <row r="321">
       <c r="B321" t="n">
-        <v>1130005</v>
+        <v>1130012</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
@@ -5281,11 +5281,11 @@
     </row>
     <row r="322">
       <c r="B322" t="n">
-        <v>1130006</v>
+        <v>1130001</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -5296,11 +5296,11 @@
     </row>
     <row r="323">
       <c r="B323" t="n">
-        <v>1130007</v>
+        <v>1130003</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -5311,11 +5311,11 @@
     </row>
     <row r="324">
       <c r="B324" t="n">
-        <v>1130010</v>
+        <v>1130004</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -5326,11 +5326,11 @@
     </row>
     <row r="325">
       <c r="B325" t="n">
-        <v>1130011</v>
+        <v>1130005</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -5341,11 +5341,11 @@
     </row>
     <row r="326">
       <c r="B326" t="n">
-        <v>1130012</v>
+        <v>1130006</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -5356,7 +5356,7 @@
     </row>
     <row r="327">
       <c r="B327" t="n">
-        <v>1130001</v>
+        <v>1130007</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
     </row>
     <row r="328">
       <c r="B328" t="n">
-        <v>1130003</v>
+        <v>1130008</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
     </row>
     <row r="329">
       <c r="B329" t="n">
-        <v>1130004</v>
+        <v>1130010</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
@@ -5395,13 +5395,13 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="B330" t="n">
-        <v>1130005</v>
+        <v>1130011</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
@@ -5410,13 +5410,13 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="B331" t="n">
-        <v>1130006</v>
+        <v>1130012</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
@@ -5425,17 +5425,17 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="B332" t="n">
-        <v>1130007</v>
+        <v>110</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -5446,11 +5446,11 @@
     </row>
     <row r="333">
       <c r="B333" t="n">
-        <v>1130008</v>
+        <v>1140001</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -5461,46 +5461,736 @@
     </row>
     <row r="334">
       <c r="B334" t="n">
-        <v>1130010</v>
+        <v>1140002</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="B335" t="n">
-        <v>1130011</v>
+        <v>1140003</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="B336" t="n">
-        <v>1130012</v>
+        <v>1140004</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="B337" t="n">
+        <v>1140005</v>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="B338" t="n">
+        <v>1140009</v>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="B339" t="n">
+        <v>1140012</v>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="B340" t="n">
+        <v>110</v>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="B341" t="n">
+        <v>1140001</v>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="B342" t="n">
+        <v>1140002</v>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="B343" t="n">
+        <v>1140003</v>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="B344" t="n">
+        <v>1140009</v>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="B345" t="n">
+        <v>1140012</v>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="B346" t="n">
+        <v>110</v>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="B347" t="n">
+        <v>1140001</v>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="B348" t="n">
+        <v>1140002</v>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="B349" t="n">
+        <v>1140003</v>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="B350" t="n">
+        <v>1140004</v>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="B351" t="n">
+        <v>1140005</v>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="B352" t="n">
+        <v>1140010</v>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="B353" t="n">
+        <v>1140004</v>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="B354" t="n">
+        <v>1140005</v>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="B355" t="n">
+        <v>1140006</v>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="B356" t="n">
+        <v>1140007</v>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="B357" t="n">
+        <v>1140008</v>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="B358" t="n">
+        <v>1140009</v>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="B359" t="n">
+        <v>1140010</v>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="B360" t="n">
+        <v>1140012</v>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="B361" t="n">
+        <v>1140001</v>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="B362" t="n">
+        <v>1140004</v>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="B363" t="n">
+        <v>1140005</v>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="B364" t="n">
+        <v>1140006</v>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="B365" t="n">
+        <v>1140007</v>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="B366" t="n">
+        <v>1140008</v>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="B367" t="n">
+        <v>1140009</v>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="B368" t="n">
+        <v>1140010</v>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="B369" t="n">
+        <v>110</v>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="B370" t="n">
+        <v>1140001</v>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="B371" t="n">
+        <v>1140006</v>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="B372" t="n">
+        <v>1140007</v>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="B373" t="n">
+        <v>1140008</v>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="B374" t="n">
+        <v>1140009</v>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="B375" t="n">
+        <v>1140012</v>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="B376" t="n">
+        <v>110</v>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
           <t>Wind</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>0.4</t>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="B377" t="n">
+        <v>1140002</v>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="B378" t="n">
+        <v>1140003</v>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="B379" t="n">
+        <v>1140006</v>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="B380" t="n">
+        <v>1140007</v>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="B381" t="n">
+        <v>1140008</v>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="B382" t="n">
+        <v>1140010</v>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>0.2</t>
         </is>
       </c>
     </row>

--- a/config/data/EnemyResistance.xlsx
+++ b/config/data/EnemyResistance.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J382"/>
+  <dimension ref="A1:J391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,26 +781,26 @@
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -811,56 +811,56 @@
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -871,7 +871,7 @@
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -880,13 +880,13 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -895,17 +895,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -916,11 +916,11 @@
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -931,11 +931,11 @@
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -946,7 +946,7 @@
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -961,11 +961,11 @@
     </row>
     <row r="34">
       <c r="B34" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -976,7 +976,7 @@
     </row>
     <row r="35">
       <c r="B35" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
     </row>
     <row r="36">
       <c r="B36" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
     </row>
     <row r="37">
       <c r="B37" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1021,26 +1021,26 @@
     </row>
     <row r="38">
       <c r="B38" t="n">
-        <v>1000001</v>
+        <v>1010001</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="n">
-        <v>1000001</v>
+        <v>1010001</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1051,11 +1051,11 @@
     </row>
     <row r="40">
       <c r="B40" t="n">
-        <v>1000001</v>
+        <v>1010001</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1066,7 +1066,7 @@
     </row>
     <row r="41">
       <c r="B41" t="n">
-        <v>1000001</v>
+        <v>1010001</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
     </row>
     <row r="42">
       <c r="B42" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1090,32 +1090,32 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1126,11 +1126,11 @@
     </row>
     <row r="45">
       <c r="B45" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1141,37 +1141,37 @@
     </row>
     <row r="46">
       <c r="B46" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1180,73 +1180,73 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1255,47 +1255,47 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1306,11 +1306,11 @@
     </row>
     <row r="57">
       <c r="B57" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1321,7 +1321,7 @@
     </row>
     <row r="58">
       <c r="B58" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1351,11 +1351,11 @@
     </row>
     <row r="60">
       <c r="B60" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1366,11 +1366,11 @@
     </row>
     <row r="61">
       <c r="B61" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1381,11 +1381,11 @@
     </row>
     <row r="62">
       <c r="B62" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1396,11 +1396,11 @@
     </row>
     <row r="63">
       <c r="B63" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1411,22 +1411,22 @@
     </row>
     <row r="64">
       <c r="B64" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1441,11 +1441,11 @@
     </row>
     <row r="66">
       <c r="B66" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -1456,11 +1456,11 @@
     </row>
     <row r="67">
       <c r="B67" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -1471,22 +1471,22 @@
     </row>
     <row r="68">
       <c r="B68" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="B69" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -1501,11 +1501,11 @@
     </row>
     <row r="70">
       <c r="B70" t="n">
-        <v>1080001</v>
+        <v>1090005</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -1516,11 +1516,11 @@
     </row>
     <row r="71">
       <c r="B71" t="n">
-        <v>1080001</v>
+        <v>1090006</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -1531,11 +1531,11 @@
     </row>
     <row r="72">
       <c r="B72" t="n">
-        <v>1080001</v>
+        <v>1090008</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -1546,11 +1546,11 @@
     </row>
     <row r="73">
       <c r="B73" t="n">
-        <v>1080001</v>
+        <v>1090009</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -1561,7 +1561,7 @@
     </row>
     <row r="74">
       <c r="B74" t="n">
-        <v>1090005</v>
+        <v>1090010</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
     </row>
     <row r="75">
       <c r="B75" t="n">
-        <v>1090006</v>
+        <v>1090012</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
     </row>
     <row r="76">
       <c r="B76" t="n">
-        <v>1090008</v>
+        <v>95</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
     </row>
     <row r="77">
       <c r="B77" t="n">
-        <v>1090009</v>
+        <v>96</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -1621,11 +1621,11 @@
     </row>
     <row r="78">
       <c r="B78" t="n">
-        <v>1090010</v>
+        <v>1090004</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -1636,11 +1636,11 @@
     </row>
     <row r="79">
       <c r="B79" t="n">
-        <v>1090012</v>
+        <v>1090005</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -1651,11 +1651,11 @@
     </row>
     <row r="80">
       <c r="B80" t="n">
-        <v>95</v>
+        <v>1090006</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -1666,11 +1666,11 @@
     </row>
     <row r="81">
       <c r="B81" t="n">
-        <v>96</v>
+        <v>1090008</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -1681,7 +1681,7 @@
     </row>
     <row r="82">
       <c r="B82" t="n">
-        <v>1090004</v>
+        <v>1090009</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
     </row>
     <row r="83">
       <c r="B83" t="n">
-        <v>1090005</v>
+        <v>1090012</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
     </row>
     <row r="84">
       <c r="B84" t="n">
-        <v>1090006</v>
+        <v>96</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -1726,11 +1726,11 @@
     </row>
     <row r="85">
       <c r="B85" t="n">
-        <v>1090008</v>
+        <v>1090002</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -1741,11 +1741,11 @@
     </row>
     <row r="86">
       <c r="B86" t="n">
-        <v>1090009</v>
+        <v>1090003</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -1756,11 +1756,11 @@
     </row>
     <row r="87">
       <c r="B87" t="n">
-        <v>1090012</v>
+        <v>1090005</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -1771,11 +1771,11 @@
     </row>
     <row r="88">
       <c r="B88" t="n">
-        <v>96</v>
+        <v>1090011</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -1786,7 +1786,7 @@
     </row>
     <row r="89">
       <c r="B89" t="n">
-        <v>1090002</v>
+        <v>1090012</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
     </row>
     <row r="90">
       <c r="B90" t="n">
-        <v>1090003</v>
+        <v>95</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
     </row>
     <row r="91">
       <c r="B91" t="n">
-        <v>1090005</v>
+        <v>1090006</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -1825,13 +1825,13 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="B92" t="n">
-        <v>1090011</v>
+        <v>96</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -1840,17 +1840,17 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="B93" t="n">
-        <v>1090012</v>
+        <v>1090002</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -1861,11 +1861,11 @@
     </row>
     <row r="94">
       <c r="B94" t="n">
-        <v>95</v>
+        <v>1090003</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -1876,31 +1876,31 @@
     </row>
     <row r="95">
       <c r="B95" t="n">
-        <v>1090006</v>
+        <v>1090004</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="B96" t="n">
-        <v>96</v>
+        <v>1090005</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -1951,11 +1951,11 @@
     </row>
     <row r="100">
       <c r="B100" t="n">
-        <v>1090005</v>
+        <v>1090006</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -1966,7 +1966,7 @@
     </row>
     <row r="101">
       <c r="B101" t="n">
-        <v>1090002</v>
+        <v>1090009</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
     </row>
     <row r="102">
       <c r="B102" t="n">
-        <v>1090003</v>
+        <v>1090010</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
     </row>
     <row r="103">
       <c r="B103" t="n">
-        <v>1090004</v>
+        <v>1090011</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="104">
       <c r="B104" t="n">
-        <v>1090006</v>
+        <v>95</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
     </row>
     <row r="105">
       <c r="B105" t="n">
-        <v>1090009</v>
+        <v>96</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -2041,11 +2041,11 @@
     </row>
     <row r="106">
       <c r="B106" t="n">
-        <v>1090010</v>
+        <v>1090002</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2056,11 +2056,11 @@
     </row>
     <row r="107">
       <c r="B107" t="n">
-        <v>1090011</v>
+        <v>1090003</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -2071,11 +2071,11 @@
     </row>
     <row r="108">
       <c r="B108" t="n">
-        <v>95</v>
+        <v>1090004</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -2086,11 +2086,11 @@
     </row>
     <row r="109">
       <c r="B109" t="n">
-        <v>96</v>
+        <v>1090008</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -2101,7 +2101,7 @@
     </row>
     <row r="110">
       <c r="B110" t="n">
-        <v>1090002</v>
+        <v>1090009</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
     </row>
     <row r="111">
       <c r="B111" t="n">
-        <v>1090003</v>
+        <v>1090010</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
     </row>
     <row r="112">
       <c r="B112" t="n">
-        <v>1090004</v>
+        <v>1090011</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
     </row>
     <row r="113">
       <c r="B113" t="n">
-        <v>1090008</v>
+        <v>1090012</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -2161,11 +2161,11 @@
     </row>
     <row r="114">
       <c r="B114" t="n">
-        <v>1090009</v>
+        <v>1090005</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -2176,11 +2176,11 @@
     </row>
     <row r="115">
       <c r="B115" t="n">
-        <v>1090010</v>
+        <v>1090008</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -2191,11 +2191,11 @@
     </row>
     <row r="116">
       <c r="B116" t="n">
-        <v>1090011</v>
+        <v>1090010</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -2206,11 +2206,11 @@
     </row>
     <row r="117">
       <c r="B117" t="n">
-        <v>1090012</v>
+        <v>1090011</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -2221,7 +2221,7 @@
     </row>
     <row r="118">
       <c r="B118" t="n">
-        <v>1090005</v>
+        <v>1090012</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
     </row>
     <row r="119">
       <c r="B119" t="n">
-        <v>1090008</v>
+        <v>95</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -2251,11 +2251,11 @@
     </row>
     <row r="120">
       <c r="B120" t="n">
-        <v>1090010</v>
+        <v>100</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -2266,11 +2266,11 @@
     </row>
     <row r="121">
       <c r="B121" t="n">
-        <v>1090011</v>
+        <v>1100002</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -2281,11 +2281,11 @@
     </row>
     <row r="122">
       <c r="B122" t="n">
-        <v>1090012</v>
+        <v>1100006</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -2296,11 +2296,11 @@
     </row>
     <row r="123">
       <c r="B123" t="n">
-        <v>95</v>
+        <v>1100007</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -2311,7 +2311,7 @@
     </row>
     <row r="124">
       <c r="B124" t="n">
-        <v>100</v>
+        <v>1100011</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
     </row>
     <row r="125">
       <c r="B125" t="n">
-        <v>1100002</v>
+        <v>1100012</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
     </row>
     <row r="126">
       <c r="B126" t="n">
-        <v>1100006</v>
+        <v>97</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
     </row>
     <row r="127">
       <c r="B127" t="n">
-        <v>1100007</v>
+        <v>99</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -2371,11 +2371,11 @@
     </row>
     <row r="128">
       <c r="B128" t="n">
-        <v>1100011</v>
+        <v>1100003</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -2386,11 +2386,11 @@
     </row>
     <row r="129">
       <c r="B129" t="n">
-        <v>1100012</v>
+        <v>1100004</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -2401,11 +2401,11 @@
     </row>
     <row r="130">
       <c r="B130" t="n">
-        <v>97</v>
+        <v>1100006</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -2416,11 +2416,11 @@
     </row>
     <row r="131">
       <c r="B131" t="n">
-        <v>99</v>
+        <v>1100009</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -2431,7 +2431,7 @@
     </row>
     <row r="132">
       <c r="B132" t="n">
-        <v>1100003</v>
+        <v>1100010</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
     </row>
     <row r="133">
       <c r="B133" t="n">
-        <v>1100004</v>
+        <v>1100011</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
     </row>
     <row r="134">
       <c r="B134" t="n">
-        <v>1100006</v>
+        <v>1100012</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
     </row>
     <row r="135">
       <c r="B135" t="n">
-        <v>1100009</v>
+        <v>97</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -2491,11 +2491,11 @@
     </row>
     <row r="136">
       <c r="B136" t="n">
-        <v>1100010</v>
+        <v>1100002</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -2506,11 +2506,11 @@
     </row>
     <row r="137">
       <c r="B137" t="n">
-        <v>1100011</v>
+        <v>1100004</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -2521,11 +2521,11 @@
     </row>
     <row r="138">
       <c r="B138" t="n">
-        <v>1100012</v>
+        <v>1100009</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -2536,11 +2536,11 @@
     </row>
     <row r="139">
       <c r="B139" t="n">
-        <v>97</v>
+        <v>1100010</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -2551,7 +2551,7 @@
     </row>
     <row r="140">
       <c r="B140" t="n">
-        <v>1100002</v>
+        <v>1100012</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
     </row>
     <row r="141">
       <c r="B141" t="n">
-        <v>1100004</v>
+        <v>97</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
     </row>
     <row r="142">
       <c r="B142" t="n">
-        <v>1100009</v>
+        <v>99</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -2596,11 +2596,11 @@
     </row>
     <row r="143">
       <c r="B143" t="n">
-        <v>1100010</v>
+        <v>100</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -2611,11 +2611,11 @@
     </row>
     <row r="144">
       <c r="B144" t="n">
-        <v>1100012</v>
+        <v>1100002</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -2626,11 +2626,11 @@
     </row>
     <row r="145">
       <c r="B145" t="n">
-        <v>97</v>
+        <v>1100003</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -2641,11 +2641,11 @@
     </row>
     <row r="146">
       <c r="B146" t="n">
-        <v>99</v>
+        <v>1100007</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -2656,7 +2656,7 @@
     </row>
     <row r="147">
       <c r="B147" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="148">
       <c r="B148" t="n">
-        <v>1100002</v>
+        <v>1100006</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -2680,17 +2680,17 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="B149" t="n">
-        <v>1100003</v>
+        <v>100</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -2701,11 +2701,11 @@
     </row>
     <row r="150">
       <c r="B150" t="n">
-        <v>1100007</v>
+        <v>1100002</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -2716,11 +2716,11 @@
     </row>
     <row r="151">
       <c r="B151" t="n">
-        <v>99</v>
+        <v>1100003</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -2731,22 +2731,22 @@
     </row>
     <row r="152">
       <c r="B152" t="n">
-        <v>1100006</v>
+        <v>1100004</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="B153" t="n">
-        <v>100</v>
+        <v>1100007</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
     </row>
     <row r="154">
       <c r="B154" t="n">
-        <v>1100002</v>
+        <v>1100009</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
     </row>
     <row r="155">
       <c r="B155" t="n">
-        <v>1100003</v>
+        <v>1100010</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
     </row>
     <row r="156">
       <c r="B156" t="n">
-        <v>1100004</v>
+        <v>1100011</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
     </row>
     <row r="157">
       <c r="B157" t="n">
-        <v>1100007</v>
+        <v>97</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -2821,11 +2821,11 @@
     </row>
     <row r="158">
       <c r="B158" t="n">
-        <v>1100009</v>
+        <v>100</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -2836,11 +2836,11 @@
     </row>
     <row r="159">
       <c r="B159" t="n">
-        <v>1100010</v>
+        <v>1100002</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -2851,11 +2851,11 @@
     </row>
     <row r="160">
       <c r="B160" t="n">
-        <v>1100011</v>
+        <v>1100003</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -2866,11 +2866,11 @@
     </row>
     <row r="161">
       <c r="B161" t="n">
-        <v>97</v>
+        <v>1100004</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -2881,7 +2881,7 @@
     </row>
     <row r="162">
       <c r="B162" t="n">
-        <v>100</v>
+        <v>1100006</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
     </row>
     <row r="163">
       <c r="B163" t="n">
-        <v>1100002</v>
+        <v>1100007</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
     </row>
     <row r="164">
       <c r="B164" t="n">
-        <v>1100003</v>
+        <v>1100009</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
     </row>
     <row r="165">
       <c r="B165" t="n">
-        <v>1100004</v>
+        <v>1100010</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
     </row>
     <row r="166">
       <c r="B166" t="n">
-        <v>1100006</v>
+        <v>1100011</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
     </row>
     <row r="167">
       <c r="B167" t="n">
-        <v>1100007</v>
+        <v>1100012</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
     </row>
     <row r="168">
       <c r="B168" t="n">
-        <v>1100009</v>
+        <v>97</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
     </row>
     <row r="169">
       <c r="B169" t="n">
-        <v>1100010</v>
+        <v>99</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -3001,11 +3001,11 @@
     </row>
     <row r="170">
       <c r="B170" t="n">
-        <v>1100011</v>
+        <v>1100006</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -3016,11 +3016,11 @@
     </row>
     <row r="171">
       <c r="B171" t="n">
-        <v>1100012</v>
+        <v>1100011</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -3031,11 +3031,11 @@
     </row>
     <row r="172">
       <c r="B172" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -3046,11 +3046,11 @@
     </row>
     <row r="173">
       <c r="B173" t="n">
-        <v>99</v>
+        <v>1110001</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -3061,11 +3061,11 @@
     </row>
     <row r="174">
       <c r="B174" t="n">
-        <v>1100006</v>
+        <v>1110002</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -3076,11 +3076,11 @@
     </row>
     <row r="175">
       <c r="B175" t="n">
-        <v>1100011</v>
+        <v>1110005</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -3091,7 +3091,7 @@
     </row>
     <row r="176">
       <c r="B176" t="n">
-        <v>102</v>
+        <v>1110006</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
     </row>
     <row r="177">
       <c r="B177" t="n">
-        <v>1110001</v>
+        <v>1110008</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
     </row>
     <row r="178">
       <c r="B178" t="n">
-        <v>1110002</v>
+        <v>103</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -3130,17 +3130,17 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="B179" t="n">
-        <v>1110005</v>
+        <v>102</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -3151,11 +3151,11 @@
     </row>
     <row r="180">
       <c r="B180" t="n">
-        <v>1110006</v>
+        <v>1110002</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -3166,11 +3166,11 @@
     </row>
     <row r="181">
       <c r="B181" t="n">
-        <v>1110008</v>
+        <v>1110003</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -3181,22 +3181,22 @@
     </row>
     <row r="182">
       <c r="B182" t="n">
-        <v>103</v>
+        <v>1110004</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="B183" t="n">
-        <v>102</v>
+        <v>1110005</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
     </row>
     <row r="184">
       <c r="B184" t="n">
-        <v>1110002</v>
+        <v>1110006</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
     </row>
     <row r="185">
       <c r="B185" t="n">
-        <v>1110003</v>
+        <v>1110008</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
     </row>
     <row r="186">
       <c r="B186" t="n">
-        <v>1110004</v>
+        <v>104</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -3250,13 +3250,13 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="B187" t="n">
-        <v>1110005</v>
+        <v>1110009</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -3265,13 +3265,13 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="B188" t="n">
-        <v>1110006</v>
+        <v>1110011</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -3280,17 +3280,17 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="B189" t="n">
-        <v>1110008</v>
+        <v>103</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -3305,48 +3305,48 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="B191" t="n">
-        <v>1110009</v>
+        <v>1110002</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="B192" t="n">
-        <v>1110011</v>
+        <v>1110005</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="B193" t="n">
-        <v>103</v>
+        <v>1110006</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
     </row>
     <row r="194">
       <c r="B194" t="n">
-        <v>104</v>
+        <v>1110009</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
     </row>
     <row r="195">
       <c r="B195" t="n">
-        <v>1110002</v>
+        <v>1110011</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -3391,11 +3391,11 @@
     </row>
     <row r="196">
       <c r="B196" t="n">
-        <v>1110005</v>
+        <v>103</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -3406,11 +3406,11 @@
     </row>
     <row r="197">
       <c r="B197" t="n">
-        <v>1110006</v>
+        <v>104</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -3421,11 +3421,11 @@
     </row>
     <row r="198">
       <c r="B198" t="n">
-        <v>1110009</v>
+        <v>1110002</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -3436,11 +3436,11 @@
     </row>
     <row r="199">
       <c r="B199" t="n">
-        <v>1110011</v>
+        <v>1110003</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -3451,7 +3451,7 @@
     </row>
     <row r="200">
       <c r="B200" t="n">
-        <v>103</v>
+        <v>1110004</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
     </row>
     <row r="201">
       <c r="B201" t="n">
-        <v>104</v>
+        <v>1110008</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
     </row>
     <row r="202">
       <c r="B202" t="n">
-        <v>1110002</v>
+        <v>1110009</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -3496,11 +3496,11 @@
     </row>
     <row r="203">
       <c r="B203" t="n">
-        <v>1110003</v>
+        <v>104</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -3511,11 +3511,11 @@
     </row>
     <row r="204">
       <c r="B204" t="n">
-        <v>1110004</v>
+        <v>1110001</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -3526,11 +3526,11 @@
     </row>
     <row r="205">
       <c r="B205" t="n">
-        <v>1110008</v>
+        <v>1110005</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -3541,11 +3541,11 @@
     </row>
     <row r="206">
       <c r="B206" t="n">
-        <v>1110009</v>
+        <v>1110006</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -3556,7 +3556,7 @@
     </row>
     <row r="207">
       <c r="B207" t="n">
-        <v>104</v>
+        <v>1110008</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
     </row>
     <row r="208">
       <c r="B208" t="n">
-        <v>1110001</v>
+        <v>1110011</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -3586,11 +3586,11 @@
     </row>
     <row r="209">
       <c r="B209" t="n">
-        <v>1110005</v>
+        <v>102</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -3601,11 +3601,11 @@
     </row>
     <row r="210">
       <c r="B210" t="n">
-        <v>1110006</v>
+        <v>103</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -3616,11 +3616,11 @@
     </row>
     <row r="211">
       <c r="B211" t="n">
-        <v>1110008</v>
+        <v>104</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -3631,11 +3631,11 @@
     </row>
     <row r="212">
       <c r="B212" t="n">
-        <v>1110011</v>
+        <v>1110001</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -3646,7 +3646,7 @@
     </row>
     <row r="213">
       <c r="B213" t="n">
-        <v>102</v>
+        <v>1110002</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
     </row>
     <row r="214">
       <c r="B214" t="n">
-        <v>103</v>
+        <v>1110003</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
     </row>
     <row r="215">
       <c r="B215" t="n">
-        <v>104</v>
+        <v>1110004</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
     </row>
     <row r="216">
       <c r="B216" t="n">
-        <v>1110001</v>
+        <v>1110008</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -3706,11 +3706,11 @@
     </row>
     <row r="217">
       <c r="B217" t="n">
-        <v>1110002</v>
+        <v>102</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -3721,11 +3721,11 @@
     </row>
     <row r="218">
       <c r="B218" t="n">
-        <v>1110003</v>
+        <v>103</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -3736,11 +3736,11 @@
     </row>
     <row r="219">
       <c r="B219" t="n">
-        <v>1110004</v>
+        <v>1110001</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -3751,11 +3751,11 @@
     </row>
     <row r="220">
       <c r="B220" t="n">
-        <v>1110008</v>
+        <v>1110003</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -3766,7 +3766,7 @@
     </row>
     <row r="221">
       <c r="B221" t="n">
-        <v>102</v>
+        <v>1110004</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
     </row>
     <row r="222">
       <c r="B222" t="n">
-        <v>103</v>
+        <v>1110005</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
     </row>
     <row r="223">
       <c r="B223" t="n">
-        <v>1110001</v>
+        <v>1110006</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
     </row>
     <row r="224">
       <c r="B224" t="n">
-        <v>1110003</v>
+        <v>1110009</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
     </row>
     <row r="225">
       <c r="B225" t="n">
-        <v>1110004</v>
+        <v>1110011</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -3841,11 +3841,11 @@
     </row>
     <row r="226">
       <c r="B226" t="n">
-        <v>1110005</v>
+        <v>108</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -3856,11 +3856,11 @@
     </row>
     <row r="227">
       <c r="B227" t="n">
-        <v>1110006</v>
+        <v>1120003</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -3871,11 +3871,11 @@
     </row>
     <row r="228">
       <c r="B228" t="n">
-        <v>1110009</v>
+        <v>1120004</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -3886,11 +3886,11 @@
     </row>
     <row r="229">
       <c r="B229" t="n">
-        <v>1110011</v>
+        <v>1120006</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -3901,7 +3901,7 @@
     </row>
     <row r="230">
       <c r="B230" t="n">
-        <v>108</v>
+        <v>1120011</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
     </row>
     <row r="231">
       <c r="B231" t="n">
-        <v>1120003</v>
+        <v>106</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -3925,17 +3925,17 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="B232" t="n">
-        <v>1120004</v>
+        <v>1120003</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -3946,11 +3946,11 @@
     </row>
     <row r="233">
       <c r="B233" t="n">
-        <v>1120006</v>
+        <v>1120004</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -3961,11 +3961,11 @@
     </row>
     <row r="234">
       <c r="B234" t="n">
-        <v>1120011</v>
+        <v>1120006</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -3976,22 +3976,22 @@
     </row>
     <row r="235">
       <c r="B235" t="n">
-        <v>106</v>
+        <v>1120007</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="B236" t="n">
-        <v>1120003</v>
+        <v>1120010</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -4006,11 +4006,11 @@
     </row>
     <row r="237">
       <c r="B237" t="n">
-        <v>1120004</v>
+        <v>107</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -4021,11 +4021,11 @@
     </row>
     <row r="238">
       <c r="B238" t="n">
-        <v>1120006</v>
+        <v>108</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -4036,11 +4036,11 @@
     </row>
     <row r="239">
       <c r="B239" t="n">
-        <v>1120007</v>
+        <v>1120001</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -4051,11 +4051,11 @@
     </row>
     <row r="240">
       <c r="B240" t="n">
-        <v>1120010</v>
+        <v>1120002</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -4066,7 +4066,7 @@
     </row>
     <row r="241">
       <c r="B241" t="n">
-        <v>107</v>
+        <v>1120003</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
     </row>
     <row r="242">
       <c r="B242" t="n">
-        <v>108</v>
+        <v>1120004</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
     </row>
     <row r="243">
       <c r="B243" t="n">
-        <v>1120001</v>
+        <v>1120010</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
     </row>
     <row r="244">
       <c r="B244" t="n">
-        <v>1120002</v>
+        <v>1120011</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
     </row>
     <row r="245">
       <c r="B245" t="n">
-        <v>1120003</v>
+        <v>1120012</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -4141,11 +4141,11 @@
     </row>
     <row r="246">
       <c r="B246" t="n">
-        <v>1120004</v>
+        <v>106</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -4156,11 +4156,11 @@
     </row>
     <row r="247">
       <c r="B247" t="n">
-        <v>1120010</v>
+        <v>107</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -4171,11 +4171,11 @@
     </row>
     <row r="248">
       <c r="B248" t="n">
-        <v>1120011</v>
+        <v>1120001</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -4186,11 +4186,11 @@
     </row>
     <row r="249">
       <c r="B249" t="n">
-        <v>1120012</v>
+        <v>1120002</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -4201,7 +4201,7 @@
     </row>
     <row r="250">
       <c r="B250" t="n">
-        <v>106</v>
+        <v>1120003</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
     </row>
     <row r="251">
       <c r="B251" t="n">
-        <v>107</v>
+        <v>1120006</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
     </row>
     <row r="252">
       <c r="B252" t="n">
-        <v>1120001</v>
+        <v>1120007</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
     </row>
     <row r="253">
       <c r="B253" t="n">
-        <v>1120002</v>
+        <v>1120010</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -4261,11 +4261,11 @@
     </row>
     <row r="254">
       <c r="B254" t="n">
-        <v>1120003</v>
+        <v>106</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -4276,11 +4276,11 @@
     </row>
     <row r="255">
       <c r="B255" t="n">
-        <v>1120006</v>
+        <v>107</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -4291,11 +4291,11 @@
     </row>
     <row r="256">
       <c r="B256" t="n">
-        <v>1120007</v>
+        <v>108</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -4306,11 +4306,11 @@
     </row>
     <row r="257">
       <c r="B257" t="n">
-        <v>1120010</v>
+        <v>1120001</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -4321,7 +4321,7 @@
     </row>
     <row r="258">
       <c r="B258" t="n">
-        <v>106</v>
+        <v>1120006</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -4336,7 +4336,7 @@
     </row>
     <row r="259">
       <c r="B259" t="n">
-        <v>107</v>
+        <v>1120010</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
     </row>
     <row r="260">
       <c r="B260" t="n">
-        <v>108</v>
+        <v>1120011</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
     </row>
     <row r="261">
       <c r="B261" t="n">
-        <v>1120001</v>
+        <v>1120012</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -4381,11 +4381,11 @@
     </row>
     <row r="262">
       <c r="B262" t="n">
-        <v>1120006</v>
+        <v>106</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -4396,11 +4396,11 @@
     </row>
     <row r="263">
       <c r="B263" t="n">
-        <v>1120010</v>
+        <v>1120001</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -4411,11 +4411,11 @@
     </row>
     <row r="264">
       <c r="B264" t="n">
-        <v>1120011</v>
+        <v>1120002</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -4426,11 +4426,11 @@
     </row>
     <row r="265">
       <c r="B265" t="n">
-        <v>1120012</v>
+        <v>1120007</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -4441,7 +4441,7 @@
     </row>
     <row r="266">
       <c r="B266" t="n">
-        <v>106</v>
+        <v>1120011</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
     </row>
     <row r="267">
       <c r="B267" t="n">
-        <v>1120001</v>
+        <v>1120012</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -4471,11 +4471,11 @@
     </row>
     <row r="268">
       <c r="B268" t="n">
-        <v>1120002</v>
+        <v>108</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -4486,11 +4486,11 @@
     </row>
     <row r="269">
       <c r="B269" t="n">
-        <v>1120007</v>
+        <v>1120001</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -4501,11 +4501,11 @@
     </row>
     <row r="270">
       <c r="B270" t="n">
-        <v>1120011</v>
+        <v>1120002</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -4516,11 +4516,11 @@
     </row>
     <row r="271">
       <c r="B271" t="n">
-        <v>1120012</v>
+        <v>1120004</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -4531,7 +4531,7 @@
     </row>
     <row r="272">
       <c r="B272" t="n">
-        <v>108</v>
+        <v>1120006</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
     </row>
     <row r="273">
       <c r="B273" t="n">
-        <v>1120001</v>
+        <v>1120007</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
     </row>
     <row r="274">
       <c r="B274" t="n">
-        <v>1120002</v>
+        <v>1120010</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
     </row>
     <row r="275">
       <c r="B275" t="n">
-        <v>1120004</v>
+        <v>1120011</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
     </row>
     <row r="276">
       <c r="B276" t="n">
-        <v>1120006</v>
+        <v>1120012</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
     </row>
     <row r="277">
       <c r="B277" t="n">
-        <v>1120007</v>
+        <v>107</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -4615,17 +4615,17 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="B278" t="n">
-        <v>1120010</v>
+        <v>1130001</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -4636,11 +4636,11 @@
     </row>
     <row r="279">
       <c r="B279" t="n">
-        <v>1120011</v>
+        <v>1130002</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -4651,11 +4651,11 @@
     </row>
     <row r="280">
       <c r="B280" t="n">
-        <v>1120012</v>
+        <v>1130006</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -4666,22 +4666,22 @@
     </row>
     <row r="281">
       <c r="B281" t="n">
-        <v>107</v>
+        <v>1130007</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="B282" t="n">
-        <v>1130001</v>
+        <v>1130008</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
     </row>
     <row r="283">
       <c r="B283" t="n">
-        <v>1130002</v>
+        <v>1130009</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
     </row>
     <row r="284">
       <c r="B284" t="n">
-        <v>1130006</v>
+        <v>1130012</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
     </row>
     <row r="285">
       <c r="B285" t="n">
-        <v>1130007</v>
+        <v>1130003</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -4735,17 +4735,17 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="B286" t="n">
-        <v>1130008</v>
+        <v>1130001</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -4756,11 +4756,11 @@
     </row>
     <row r="287">
       <c r="B287" t="n">
-        <v>1130009</v>
+        <v>1130002</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -4771,11 +4771,11 @@
     </row>
     <row r="288">
       <c r="B288" t="n">
-        <v>1130012</v>
+        <v>1130009</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -4786,26 +4786,26 @@
     </row>
     <row r="289">
       <c r="B289" t="n">
-        <v>1130003</v>
+        <v>1130007</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="B290" t="n">
-        <v>1130001</v>
+        <v>1130008</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -4816,11 +4816,11 @@
     </row>
     <row r="291">
       <c r="B291" t="n">
-        <v>1130002</v>
+        <v>1130009</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -4831,11 +4831,11 @@
     </row>
     <row r="292">
       <c r="B292" t="n">
-        <v>1130009</v>
+        <v>1130012</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -4846,11 +4846,11 @@
     </row>
     <row r="293">
       <c r="B293" t="n">
-        <v>1130007</v>
+        <v>1130002</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -4861,11 +4861,11 @@
     </row>
     <row r="294">
       <c r="B294" t="n">
-        <v>1130008</v>
+        <v>1130004</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -4876,11 +4876,11 @@
     </row>
     <row r="295">
       <c r="B295" t="n">
-        <v>1130009</v>
+        <v>1130005</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -4891,11 +4891,11 @@
     </row>
     <row r="296">
       <c r="B296" t="n">
-        <v>1130012</v>
+        <v>1130006</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -4906,7 +4906,7 @@
     </row>
     <row r="297">
       <c r="B297" t="n">
-        <v>1130002</v>
+        <v>1130007</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
     </row>
     <row r="298">
       <c r="B298" t="n">
-        <v>1130004</v>
+        <v>1130008</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
     </row>
     <row r="299">
       <c r="B299" t="n">
-        <v>1130005</v>
+        <v>1130009</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
     </row>
     <row r="300">
       <c r="B300" t="n">
-        <v>1130006</v>
+        <v>1130010</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
     </row>
     <row r="301">
       <c r="B301" t="n">
-        <v>1130007</v>
+        <v>1130011</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -4981,11 +4981,11 @@
     </row>
     <row r="302">
       <c r="B302" t="n">
-        <v>1130008</v>
+        <v>1130001</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -4996,11 +4996,11 @@
     </row>
     <row r="303">
       <c r="B303" t="n">
-        <v>1130009</v>
+        <v>1130003</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -5011,11 +5011,11 @@
     </row>
     <row r="304">
       <c r="B304" t="n">
-        <v>1130010</v>
+        <v>1130004</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -5026,11 +5026,11 @@
     </row>
     <row r="305">
       <c r="B305" t="n">
-        <v>1130011</v>
+        <v>1130005</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -5041,7 +5041,7 @@
     </row>
     <row r="306">
       <c r="B306" t="n">
-        <v>1130001</v>
+        <v>1130009</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
     </row>
     <row r="307">
       <c r="B307" t="n">
-        <v>1130003</v>
+        <v>1130010</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
     </row>
     <row r="308">
       <c r="B308" t="n">
-        <v>1130004</v>
+        <v>1130011</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -5086,11 +5086,11 @@
     </row>
     <row r="309">
       <c r="B309" t="n">
-        <v>1130005</v>
+        <v>1130002</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -5101,11 +5101,11 @@
     </row>
     <row r="310">
       <c r="B310" t="n">
-        <v>1130009</v>
+        <v>1130003</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -5116,11 +5116,11 @@
     </row>
     <row r="311">
       <c r="B311" t="n">
-        <v>1130010</v>
+        <v>1130004</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -5131,11 +5131,11 @@
     </row>
     <row r="312">
       <c r="B312" t="n">
-        <v>1130011</v>
+        <v>1130005</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -5146,7 +5146,7 @@
     </row>
     <row r="313">
       <c r="B313" t="n">
-        <v>1130002</v>
+        <v>1130006</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
     </row>
     <row r="314">
       <c r="B314" t="n">
-        <v>1130003</v>
+        <v>1130007</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
     </row>
     <row r="315">
       <c r="B315" t="n">
-        <v>1130004</v>
+        <v>1130010</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
     </row>
     <row r="316">
       <c r="B316" t="n">
-        <v>1130005</v>
+        <v>1130011</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
@@ -5206,7 +5206,7 @@
     </row>
     <row r="317">
       <c r="B317" t="n">
-        <v>1130006</v>
+        <v>1130012</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
@@ -5221,11 +5221,11 @@
     </row>
     <row r="318">
       <c r="B318" t="n">
-        <v>1130007</v>
+        <v>1130001</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -5236,11 +5236,11 @@
     </row>
     <row r="319">
       <c r="B319" t="n">
-        <v>1130010</v>
+        <v>1130003</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -5251,11 +5251,11 @@
     </row>
     <row r="320">
       <c r="B320" t="n">
-        <v>1130011</v>
+        <v>1130004</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -5266,11 +5266,11 @@
     </row>
     <row r="321">
       <c r="B321" t="n">
-        <v>1130012</v>
+        <v>1130005</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -5281,7 +5281,7 @@
     </row>
     <row r="322">
       <c r="B322" t="n">
-        <v>1130001</v>
+        <v>1130006</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
     </row>
     <row r="323">
       <c r="B323" t="n">
-        <v>1130003</v>
+        <v>1130007</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
     </row>
     <row r="324">
       <c r="B324" t="n">
-        <v>1130004</v>
+        <v>1130008</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
     </row>
     <row r="325">
       <c r="B325" t="n">
-        <v>1130005</v>
+        <v>1130010</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
@@ -5335,13 +5335,13 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="B326" t="n">
-        <v>1130006</v>
+        <v>1130011</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
@@ -5350,13 +5350,13 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="B327" t="n">
-        <v>1130007</v>
+        <v>1130012</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
@@ -5365,17 +5365,17 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="B328" t="n">
-        <v>1130008</v>
+        <v>110</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -5386,52 +5386,52 @@
     </row>
     <row r="329">
       <c r="B329" t="n">
-        <v>1130010</v>
+        <v>1140001</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="B330" t="n">
-        <v>1130011</v>
+        <v>1140002</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="B331" t="n">
-        <v>1130012</v>
+        <v>1140003</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="B332" t="n">
-        <v>110</v>
+        <v>1140004</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
     </row>
     <row r="333">
       <c r="B333" t="n">
-        <v>1140001</v>
+        <v>1140005</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
     </row>
     <row r="334">
       <c r="B334" t="n">
-        <v>1140002</v>
+        <v>1140009</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
     </row>
     <row r="335">
       <c r="B335" t="n">
-        <v>1140003</v>
+        <v>1140012</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
@@ -5491,11 +5491,11 @@
     </row>
     <row r="336">
       <c r="B336" t="n">
-        <v>1140004</v>
+        <v>110</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -5506,11 +5506,11 @@
     </row>
     <row r="337">
       <c r="B337" t="n">
-        <v>1140005</v>
+        <v>1140001</v>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -5521,11 +5521,11 @@
     </row>
     <row r="338">
       <c r="B338" t="n">
-        <v>1140009</v>
+        <v>1140002</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -5536,11 +5536,11 @@
     </row>
     <row r="339">
       <c r="B339" t="n">
-        <v>1140012</v>
+        <v>1140003</v>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -5551,7 +5551,7 @@
     </row>
     <row r="340">
       <c r="B340" t="n">
-        <v>110</v>
+        <v>1140009</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
     </row>
     <row r="341">
       <c r="B341" t="n">
-        <v>1140001</v>
+        <v>1140012</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
@@ -5581,11 +5581,11 @@
     </row>
     <row r="342">
       <c r="B342" t="n">
-        <v>1140002</v>
+        <v>110</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -5596,11 +5596,11 @@
     </row>
     <row r="343">
       <c r="B343" t="n">
-        <v>1140003</v>
+        <v>1140001</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -5611,11 +5611,11 @@
     </row>
     <row r="344">
       <c r="B344" t="n">
-        <v>1140009</v>
+        <v>1140002</v>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -5626,11 +5626,11 @@
     </row>
     <row r="345">
       <c r="B345" t="n">
-        <v>1140012</v>
+        <v>1140003</v>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -5641,7 +5641,7 @@
     </row>
     <row r="346">
       <c r="B346" t="n">
-        <v>110</v>
+        <v>1140004</v>
       </c>
       <c r="C346" t="inlineStr">
         <is>
@@ -5656,7 +5656,7 @@
     </row>
     <row r="347">
       <c r="B347" t="n">
-        <v>1140001</v>
+        <v>1140005</v>
       </c>
       <c r="C347" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
     </row>
     <row r="348">
       <c r="B348" t="n">
-        <v>1140002</v>
+        <v>1140010</v>
       </c>
       <c r="C348" t="inlineStr">
         <is>
@@ -5686,11 +5686,11 @@
     </row>
     <row r="349">
       <c r="B349" t="n">
-        <v>1140003</v>
+        <v>1140004</v>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -5701,11 +5701,11 @@
     </row>
     <row r="350">
       <c r="B350" t="n">
-        <v>1140004</v>
+        <v>1140005</v>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -5716,11 +5716,11 @@
     </row>
     <row r="351">
       <c r="B351" t="n">
-        <v>1140005</v>
+        <v>1140006</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -5731,11 +5731,11 @@
     </row>
     <row r="352">
       <c r="B352" t="n">
-        <v>1140010</v>
+        <v>1140007</v>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -5746,7 +5746,7 @@
     </row>
     <row r="353">
       <c r="B353" t="n">
-        <v>1140004</v>
+        <v>1140008</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
     </row>
     <row r="354">
       <c r="B354" t="n">
-        <v>1140005</v>
+        <v>1140009</v>
       </c>
       <c r="C354" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
     </row>
     <row r="355">
       <c r="B355" t="n">
-        <v>1140006</v>
+        <v>1140010</v>
       </c>
       <c r="C355" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
     </row>
     <row r="356">
       <c r="B356" t="n">
-        <v>1140007</v>
+        <v>1140012</v>
       </c>
       <c r="C356" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
     </row>
     <row r="357">
       <c r="B357" t="n">
-        <v>1140008</v>
+        <v>1140001</v>
       </c>
       <c r="C357" t="inlineStr">
         <is>
@@ -5815,17 +5815,17 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="B358" t="n">
-        <v>1140009</v>
+        <v>1140004</v>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -5836,11 +5836,11 @@
     </row>
     <row r="359">
       <c r="B359" t="n">
-        <v>1140010</v>
+        <v>1140005</v>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -5851,11 +5851,11 @@
     </row>
     <row r="360">
       <c r="B360" t="n">
-        <v>1140012</v>
+        <v>1140006</v>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -5866,22 +5866,22 @@
     </row>
     <row r="361">
       <c r="B361" t="n">
-        <v>1140001</v>
+        <v>1140007</v>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="B362" t="n">
-        <v>1140004</v>
+        <v>1140008</v>
       </c>
       <c r="C362" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
     </row>
     <row r="363">
       <c r="B363" t="n">
-        <v>1140005</v>
+        <v>1140009</v>
       </c>
       <c r="C363" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
     </row>
     <row r="364">
       <c r="B364" t="n">
-        <v>1140006</v>
+        <v>1140010</v>
       </c>
       <c r="C364" t="inlineStr">
         <is>
@@ -5926,11 +5926,11 @@
     </row>
     <row r="365">
       <c r="B365" t="n">
-        <v>1140007</v>
+        <v>110</v>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -5941,11 +5941,11 @@
     </row>
     <row r="366">
       <c r="B366" t="n">
-        <v>1140008</v>
+        <v>1140001</v>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -5956,11 +5956,11 @@
     </row>
     <row r="367">
       <c r="B367" t="n">
-        <v>1140009</v>
+        <v>1140006</v>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -5971,11 +5971,11 @@
     </row>
     <row r="368">
       <c r="B368" t="n">
-        <v>1140010</v>
+        <v>1140007</v>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -5986,7 +5986,7 @@
     </row>
     <row r="369">
       <c r="B369" t="n">
-        <v>110</v>
+        <v>1140008</v>
       </c>
       <c r="C369" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
     </row>
     <row r="370">
       <c r="B370" t="n">
-        <v>1140001</v>
+        <v>1140009</v>
       </c>
       <c r="C370" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
     </row>
     <row r="371">
       <c r="B371" t="n">
-        <v>1140006</v>
+        <v>1140012</v>
       </c>
       <c r="C371" t="inlineStr">
         <is>
@@ -6031,11 +6031,11 @@
     </row>
     <row r="372">
       <c r="B372" t="n">
-        <v>1140007</v>
+        <v>110</v>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -6046,11 +6046,11 @@
     </row>
     <row r="373">
       <c r="B373" t="n">
-        <v>1140008</v>
+        <v>1140002</v>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -6061,11 +6061,11 @@
     </row>
     <row r="374">
       <c r="B374" t="n">
-        <v>1140009</v>
+        <v>1140003</v>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -6076,11 +6076,11 @@
     </row>
     <row r="375">
       <c r="B375" t="n">
-        <v>1140012</v>
+        <v>1140006</v>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -6091,7 +6091,7 @@
     </row>
     <row r="376">
       <c r="B376" t="n">
-        <v>110</v>
+        <v>1140007</v>
       </c>
       <c r="C376" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
     </row>
     <row r="377">
       <c r="B377" t="n">
-        <v>1140002</v>
+        <v>1140008</v>
       </c>
       <c r="C377" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
     </row>
     <row r="378">
       <c r="B378" t="n">
-        <v>1140003</v>
+        <v>1140010</v>
       </c>
       <c r="C378" t="inlineStr">
         <is>
@@ -6136,11 +6136,11 @@
     </row>
     <row r="379">
       <c r="B379" t="n">
-        <v>1140006</v>
+        <v>111</v>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -6151,11 +6151,11 @@
     </row>
     <row r="380">
       <c r="B380" t="n">
-        <v>1140007</v>
+        <v>1150003</v>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -6166,11 +6166,11 @@
     </row>
     <row r="381">
       <c r="B381" t="n">
-        <v>1140008</v>
+        <v>111</v>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -6181,16 +6181,151 @@
     </row>
     <row r="382">
       <c r="B382" t="n">
-        <v>1140010</v>
+        <v>1150002</v>
       </c>
       <c r="C382" t="inlineStr">
         <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="B383" t="n">
+        <v>1150002</v>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="B384" t="n">
+        <v>1150003</v>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="B385" t="n">
+        <v>111</v>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="B386" t="n">
+        <v>1150003</v>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="B387" t="n">
+        <v>1150002</v>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="B388" t="n">
+        <v>111</v>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="B389" t="n">
+        <v>1150002</v>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="B390" t="n">
+        <v>1150003</v>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="B391" t="n">
+        <v>1150002</v>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
           <t>Wind</t>
         </is>
       </c>
-      <c r="D382" t="inlineStr">
-        <is>
-          <t>0.2</t>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>0.4</t>
         </is>
       </c>
     </row>

--- a/config/data/EnemyResistance.xlsx
+++ b/config/data/EnemyResistance.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:J391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -571,7 +571,7 @@
     </row>
     <row r="8">
       <c r="B8" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -586,26 +586,26 @@
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -616,11 +616,11 @@
     </row>
     <row r="11">
       <c r="B11" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -646,7 +646,7 @@
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -661,11 +661,11 @@
     </row>
     <row r="14">
       <c r="B14" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -676,11 +676,11 @@
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -691,11 +691,11 @@
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -706,11 +706,11 @@
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -721,11 +721,11 @@
     </row>
     <row r="18">
       <c r="B18" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -736,11 +736,11 @@
     </row>
     <row r="19">
       <c r="B19" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -751,11 +751,11 @@
     </row>
     <row r="20">
       <c r="B20" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -766,41 +766,41 @@
     </row>
     <row r="21">
       <c r="B21" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -811,22 +811,22 @@
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -835,32 +835,32 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>104</v>
+        <v>980001</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>104</v>
+        <v>980001</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -871,11 +871,11 @@
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>104</v>
+        <v>980001</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -886,11 +886,11 @@
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>104</v>
+        <v>980001</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -901,11 +901,11 @@
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>104</v>
+        <v>990001</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -916,11 +916,11 @@
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>105</v>
+        <v>990001</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -931,11 +931,11 @@
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>105</v>
+        <v>990001</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -946,11 +946,11 @@
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>105</v>
+        <v>990001</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -961,11 +961,11 @@
     </row>
     <row r="34">
       <c r="B34" t="n">
-        <v>105</v>
+        <v>1000001</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -976,26 +976,26 @@
     </row>
     <row r="35">
       <c r="B35" t="n">
-        <v>106</v>
+        <v>1000001</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="n">
-        <v>106</v>
+        <v>1000001</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1006,11 +1006,11 @@
     </row>
     <row r="37">
       <c r="B37" t="n">
-        <v>106</v>
+        <v>1000001</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1021,22 +1021,22 @@
     </row>
     <row r="38">
       <c r="B38" t="n">
-        <v>106</v>
+        <v>1010001</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="n">
-        <v>107</v>
+        <v>1010001</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
     </row>
     <row r="40">
       <c r="B40" t="n">
-        <v>107</v>
+        <v>1010001</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1066,11 +1066,11 @@
     </row>
     <row r="41">
       <c r="B41" t="n">
-        <v>107</v>
+        <v>1010001</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1081,41 +1081,41 @@
     </row>
     <row r="42">
       <c r="B42" t="n">
-        <v>107</v>
+        <v>1020001</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="n">
-        <v>108</v>
+        <v>1020001</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="n">
-        <v>108</v>
+        <v>1020001</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1126,11 +1126,11 @@
     </row>
     <row r="45">
       <c r="B45" t="n">
-        <v>108</v>
+        <v>1020001</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1141,26 +1141,26 @@
     </row>
     <row r="46">
       <c r="B46" t="n">
-        <v>108</v>
+        <v>1030001</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" t="n">
-        <v>109</v>
+        <v>1030001</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1171,41 +1171,41 @@
     </row>
     <row r="48">
       <c r="B48" t="n">
-        <v>109</v>
+        <v>1030001</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" t="n">
-        <v>109</v>
+        <v>1030001</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" t="n">
-        <v>109</v>
+        <v>1040001</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1216,26 +1216,26 @@
     </row>
     <row r="51">
       <c r="B51" t="n">
-        <v>109</v>
+        <v>1040001</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" t="n">
-        <v>110</v>
+        <v>1040001</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1246,11 +1246,11 @@
     </row>
     <row r="53">
       <c r="B53" t="n">
-        <v>110</v>
+        <v>1040001</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1261,26 +1261,26 @@
     </row>
     <row r="54">
       <c r="B54" t="n">
-        <v>110</v>
+        <v>1050001</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" t="n">
-        <v>110</v>
+        <v>1050001</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Imaginary</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1291,11 +1291,11 @@
     </row>
     <row r="56">
       <c r="B56" t="n">
-        <v>110</v>
+        <v>1050001</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1306,11 +1306,11 @@
     </row>
     <row r="57">
       <c r="B57" t="n">
-        <v>111</v>
+        <v>1050001</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1321,7 +1321,7 @@
     </row>
     <row r="58">
       <c r="B58" t="n">
-        <v>111</v>
+        <v>1060001</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
     </row>
     <row r="59">
       <c r="B59" t="n">
-        <v>111</v>
+        <v>1060001</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1351,11 +1351,11 @@
     </row>
     <row r="60">
       <c r="B60" t="n">
-        <v>111</v>
+        <v>1060001</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1366,11 +1366,11 @@
     </row>
     <row r="61">
       <c r="B61" t="n">
-        <v>95</v>
+        <v>1060001</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1381,11 +1381,11 @@
     </row>
     <row r="62">
       <c r="B62" t="n">
-        <v>95</v>
+        <v>1070001</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1396,11 +1396,11 @@
     </row>
     <row r="63">
       <c r="B63" t="n">
-        <v>95</v>
+        <v>1070001</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1411,26 +1411,26 @@
     </row>
     <row r="64">
       <c r="B64" t="n">
-        <v>95</v>
+        <v>1070001</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" t="n">
-        <v>96</v>
+        <v>1070001</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1441,7 +1441,7 @@
     </row>
     <row r="66">
       <c r="B66" t="n">
-        <v>96</v>
+        <v>1080001</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
     </row>
     <row r="67">
       <c r="B67" t="n">
-        <v>96</v>
+        <v>1080001</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -1465,13 +1465,13 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="B68" t="n">
-        <v>96</v>
+        <v>1080001</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -1486,11 +1486,11 @@
     </row>
     <row r="69">
       <c r="B69" t="n">
-        <v>97</v>
+        <v>1080001</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -1501,11 +1501,11 @@
     </row>
     <row r="70">
       <c r="B70" t="n">
-        <v>97</v>
+        <v>1090005</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -1516,11 +1516,11 @@
     </row>
     <row r="71">
       <c r="B71" t="n">
-        <v>97</v>
+        <v>1090006</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -1531,11 +1531,11 @@
     </row>
     <row r="72">
       <c r="B72" t="n">
-        <v>97</v>
+        <v>1090008</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -1546,11 +1546,11 @@
     </row>
     <row r="73">
       <c r="B73" t="n">
-        <v>97</v>
+        <v>1090009</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -1561,26 +1561,26 @@
     </row>
     <row r="74">
       <c r="B74" t="n">
-        <v>98</v>
+        <v>1090010</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="B75" t="n">
-        <v>98</v>
+        <v>1090012</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -1591,41 +1591,41 @@
     </row>
     <row r="76">
       <c r="B76" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="B77" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="B78" t="n">
-        <v>99</v>
+        <v>1090004</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -1636,11 +1636,11 @@
     </row>
     <row r="79">
       <c r="B79" t="n">
-        <v>99</v>
+        <v>1090005</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Imaginary</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -1651,11 +1651,11 @@
     </row>
     <row r="80">
       <c r="B80" t="n">
-        <v>99</v>
+        <v>1090006</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -1666,16 +1666,4666 @@
     </row>
     <row r="81">
       <c r="B81" t="n">
+        <v>1090008</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="n">
+        <v>1090009</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="n">
+        <v>1090012</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="n">
+        <v>96</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="n">
+        <v>1090002</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="n">
+        <v>1090003</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="n">
+        <v>1090005</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="n">
+        <v>1090011</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="n">
+        <v>1090012</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="n">
+        <v>95</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="n">
+        <v>1090006</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="n">
+        <v>96</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="n">
+        <v>1090002</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="n">
+        <v>1090003</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="n">
+        <v>1090004</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="n">
+        <v>1090005</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="n">
+        <v>1090002</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="n">
+        <v>1090003</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="n">
+        <v>1090004</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="n">
+        <v>1090006</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="n">
+        <v>1090009</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="n">
+        <v>1090010</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="n">
+        <v>1090011</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" t="n">
+        <v>95</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="n">
+        <v>96</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="n">
+        <v>1090002</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" t="n">
+        <v>1090003</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" t="n">
+        <v>1090004</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" t="n">
+        <v>1090008</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" t="n">
+        <v>1090009</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" t="n">
+        <v>1090010</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" t="n">
+        <v>1090011</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" t="n">
+        <v>1090012</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" t="n">
+        <v>1090005</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" t="n">
+        <v>1090008</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" t="n">
+        <v>1090010</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" t="n">
+        <v>1090011</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" t="n">
+        <v>1090012</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" t="n">
+        <v>95</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" t="n">
+        <v>100</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" t="n">
+        <v>1100002</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" t="n">
+        <v>1100006</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" t="n">
+        <v>1100007</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" t="n">
+        <v>1100011</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" t="n">
+        <v>1100012</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" t="n">
+        <v>97</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" t="n">
         <v>99</v>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" t="n">
+        <v>1100003</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" t="n">
+        <v>1100004</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" t="n">
+        <v>1100006</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" t="n">
+        <v>1100009</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" t="n">
+        <v>1100010</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" t="n">
+        <v>1100011</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" t="n">
+        <v>1100012</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" t="n">
+        <v>97</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" t="n">
+        <v>1100002</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" t="n">
+        <v>1100004</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" t="n">
+        <v>1100009</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" t="n">
+        <v>1100010</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" t="n">
+        <v>1100012</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" t="n">
+        <v>97</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" t="n">
+        <v>99</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" t="n">
+        <v>100</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" t="n">
+        <v>1100002</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" t="n">
+        <v>1100003</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" t="n">
+        <v>1100007</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" t="n">
+        <v>99</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" t="n">
+        <v>1100006</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" t="n">
+        <v>100</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" t="n">
+        <v>1100002</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" t="n">
+        <v>1100003</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" t="n">
+        <v>1100004</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" t="n">
+        <v>1100007</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" t="n">
+        <v>1100009</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" t="n">
+        <v>1100010</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" t="n">
+        <v>1100011</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" t="n">
+        <v>97</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" t="n">
+        <v>100</v>
+      </c>
+      <c r="C158" t="inlineStr">
         <is>
           <t>Quantum</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>0.2</t>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" t="n">
+        <v>1100002</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" t="n">
+        <v>1100003</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" t="n">
+        <v>1100004</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" t="n">
+        <v>1100006</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" t="n">
+        <v>1100007</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" t="n">
+        <v>1100009</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" t="n">
+        <v>1100010</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" t="n">
+        <v>1100011</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" t="n">
+        <v>1100012</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" t="n">
+        <v>97</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" t="n">
+        <v>99</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" t="n">
+        <v>1100006</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" t="n">
+        <v>1100011</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" t="n">
+        <v>102</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" t="n">
+        <v>1110001</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" t="n">
+        <v>1110002</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" t="n">
+        <v>1110005</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" t="n">
+        <v>1110006</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" t="n">
+        <v>1110008</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" t="n">
+        <v>103</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" t="n">
+        <v>102</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" t="n">
+        <v>1110002</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" t="n">
+        <v>1110003</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" t="n">
+        <v>1110004</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" t="n">
+        <v>1110005</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="B184" t="n">
+        <v>1110006</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" t="n">
+        <v>1110008</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" t="n">
+        <v>104</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" t="n">
+        <v>1110009</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" t="n">
+        <v>1110011</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" t="n">
+        <v>103</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" t="n">
+        <v>104</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="B191" t="n">
+        <v>1110002</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="B192" t="n">
+        <v>1110005</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="B193" t="n">
+        <v>1110006</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="B194" t="n">
+        <v>1110009</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="B195" t="n">
+        <v>1110011</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="B196" t="n">
+        <v>103</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="B197" t="n">
+        <v>104</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="B198" t="n">
+        <v>1110002</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="B199" t="n">
+        <v>1110003</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="B200" t="n">
+        <v>1110004</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="B201" t="n">
+        <v>1110008</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="B202" t="n">
+        <v>1110009</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="B203" t="n">
+        <v>104</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="B204" t="n">
+        <v>1110001</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="B205" t="n">
+        <v>1110005</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="B206" t="n">
+        <v>1110006</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="B207" t="n">
+        <v>1110008</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="B208" t="n">
+        <v>1110011</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="B209" t="n">
+        <v>102</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="B210" t="n">
+        <v>103</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="B211" t="n">
+        <v>104</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="B212" t="n">
+        <v>1110001</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="B213" t="n">
+        <v>1110002</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="B214" t="n">
+        <v>1110003</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="B215" t="n">
+        <v>1110004</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="B216" t="n">
+        <v>1110008</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="B217" t="n">
+        <v>102</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="B218" t="n">
+        <v>103</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="B219" t="n">
+        <v>1110001</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="B220" t="n">
+        <v>1110003</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="B221" t="n">
+        <v>1110004</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="B222" t="n">
+        <v>1110005</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="B223" t="n">
+        <v>1110006</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="B224" t="n">
+        <v>1110009</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="B225" t="n">
+        <v>1110011</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="B226" t="n">
+        <v>108</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="B227" t="n">
+        <v>1120003</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="B228" t="n">
+        <v>1120004</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="B229" t="n">
+        <v>1120006</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="B230" t="n">
+        <v>1120011</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="B231" t="n">
+        <v>106</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="B232" t="n">
+        <v>1120003</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="B233" t="n">
+        <v>1120004</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="B234" t="n">
+        <v>1120006</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="B235" t="n">
+        <v>1120007</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="B236" t="n">
+        <v>1120010</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="B237" t="n">
+        <v>107</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="B238" t="n">
+        <v>108</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="B239" t="n">
+        <v>1120001</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="B240" t="n">
+        <v>1120002</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="B241" t="n">
+        <v>1120003</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="B242" t="n">
+        <v>1120004</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="B243" t="n">
+        <v>1120010</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="B244" t="n">
+        <v>1120011</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="B245" t="n">
+        <v>1120012</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="B246" t="n">
+        <v>106</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="B247" t="n">
+        <v>107</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="B248" t="n">
+        <v>1120001</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="B249" t="n">
+        <v>1120002</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="B250" t="n">
+        <v>1120003</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="B251" t="n">
+        <v>1120006</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="B252" t="n">
+        <v>1120007</v>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="B253" t="n">
+        <v>1120010</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="B254" t="n">
+        <v>106</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="B255" t="n">
+        <v>107</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="B256" t="n">
+        <v>108</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="B257" t="n">
+        <v>1120001</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="B258" t="n">
+        <v>1120006</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="B259" t="n">
+        <v>1120010</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="B260" t="n">
+        <v>1120011</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="B261" t="n">
+        <v>1120012</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="B262" t="n">
+        <v>106</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="B263" t="n">
+        <v>1120001</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="B264" t="n">
+        <v>1120002</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="B265" t="n">
+        <v>1120007</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="B266" t="n">
+        <v>1120011</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="B267" t="n">
+        <v>1120012</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="B268" t="n">
+        <v>108</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="B269" t="n">
+        <v>1120001</v>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="B270" t="n">
+        <v>1120002</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="B271" t="n">
+        <v>1120004</v>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="B272" t="n">
+        <v>1120006</v>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="B273" t="n">
+        <v>1120007</v>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="B274" t="n">
+        <v>1120010</v>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="B275" t="n">
+        <v>1120011</v>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="B276" t="n">
+        <v>1120012</v>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="B277" t="n">
+        <v>107</v>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="B278" t="n">
+        <v>1130001</v>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="B279" t="n">
+        <v>1130002</v>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="B280" t="n">
+        <v>1130006</v>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="B281" t="n">
+        <v>1130007</v>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="B282" t="n">
+        <v>1130008</v>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="B283" t="n">
+        <v>1130009</v>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="B284" t="n">
+        <v>1130012</v>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="B285" t="n">
+        <v>1130003</v>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="B286" t="n">
+        <v>1130001</v>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="B287" t="n">
+        <v>1130002</v>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="B288" t="n">
+        <v>1130009</v>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="B289" t="n">
+        <v>1130007</v>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="B290" t="n">
+        <v>1130008</v>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="B291" t="n">
+        <v>1130009</v>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="B292" t="n">
+        <v>1130012</v>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="B293" t="n">
+        <v>1130002</v>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="B294" t="n">
+        <v>1130004</v>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="B295" t="n">
+        <v>1130005</v>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="B296" t="n">
+        <v>1130006</v>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="B297" t="n">
+        <v>1130007</v>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="B298" t="n">
+        <v>1130008</v>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="B299" t="n">
+        <v>1130009</v>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="B300" t="n">
+        <v>1130010</v>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="B301" t="n">
+        <v>1130011</v>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="B302" t="n">
+        <v>1130001</v>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="B303" t="n">
+        <v>1130003</v>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="B304" t="n">
+        <v>1130004</v>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="B305" t="n">
+        <v>1130005</v>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="B306" t="n">
+        <v>1130009</v>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="B307" t="n">
+        <v>1130010</v>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="B308" t="n">
+        <v>1130011</v>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="B309" t="n">
+        <v>1130002</v>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="B310" t="n">
+        <v>1130003</v>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="B311" t="n">
+        <v>1130004</v>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="B312" t="n">
+        <v>1130005</v>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="B313" t="n">
+        <v>1130006</v>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="B314" t="n">
+        <v>1130007</v>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="B315" t="n">
+        <v>1130010</v>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="B316" t="n">
+        <v>1130011</v>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="B317" t="n">
+        <v>1130012</v>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="B318" t="n">
+        <v>1130001</v>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="B319" t="n">
+        <v>1130003</v>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="B320" t="n">
+        <v>1130004</v>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="B321" t="n">
+        <v>1130005</v>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="B322" t="n">
+        <v>1130006</v>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="B323" t="n">
+        <v>1130007</v>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="B324" t="n">
+        <v>1130008</v>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="B325" t="n">
+        <v>1130010</v>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="B326" t="n">
+        <v>1130011</v>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="B327" t="n">
+        <v>1130012</v>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="B328" t="n">
+        <v>110</v>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="B329" t="n">
+        <v>1140001</v>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="B330" t="n">
+        <v>1140002</v>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="B331" t="n">
+        <v>1140003</v>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="B332" t="n">
+        <v>1140004</v>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="B333" t="n">
+        <v>1140005</v>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="B334" t="n">
+        <v>1140009</v>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="B335" t="n">
+        <v>1140012</v>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="B336" t="n">
+        <v>110</v>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="B337" t="n">
+        <v>1140001</v>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="B338" t="n">
+        <v>1140002</v>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="B339" t="n">
+        <v>1140003</v>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="B340" t="n">
+        <v>1140009</v>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="B341" t="n">
+        <v>1140012</v>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="B342" t="n">
+        <v>110</v>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="B343" t="n">
+        <v>1140001</v>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="B344" t="n">
+        <v>1140002</v>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="B345" t="n">
+        <v>1140003</v>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="B346" t="n">
+        <v>1140004</v>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="B347" t="n">
+        <v>1140005</v>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="B348" t="n">
+        <v>1140010</v>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="B349" t="n">
+        <v>1140004</v>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="B350" t="n">
+        <v>1140005</v>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="B351" t="n">
+        <v>1140006</v>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="B352" t="n">
+        <v>1140007</v>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="B353" t="n">
+        <v>1140008</v>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="B354" t="n">
+        <v>1140009</v>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="B355" t="n">
+        <v>1140010</v>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="B356" t="n">
+        <v>1140012</v>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="B357" t="n">
+        <v>1140001</v>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="B358" t="n">
+        <v>1140004</v>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="B359" t="n">
+        <v>1140005</v>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="B360" t="n">
+        <v>1140006</v>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="B361" t="n">
+        <v>1140007</v>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="B362" t="n">
+        <v>1140008</v>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="B363" t="n">
+        <v>1140009</v>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="B364" t="n">
+        <v>1140010</v>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="B365" t="n">
+        <v>110</v>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="B366" t="n">
+        <v>1140001</v>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="B367" t="n">
+        <v>1140006</v>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="B368" t="n">
+        <v>1140007</v>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="B369" t="n">
+        <v>1140008</v>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="B370" t="n">
+        <v>1140009</v>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="B371" t="n">
+        <v>1140012</v>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="B372" t="n">
+        <v>110</v>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="B373" t="n">
+        <v>1140002</v>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="B374" t="n">
+        <v>1140003</v>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="B375" t="n">
+        <v>1140006</v>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="B376" t="n">
+        <v>1140007</v>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="B377" t="n">
+        <v>1140008</v>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="B378" t="n">
+        <v>1140010</v>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="B379" t="n">
+        <v>111</v>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="B380" t="n">
+        <v>1150003</v>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="B381" t="n">
+        <v>111</v>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="B382" t="n">
+        <v>1150002</v>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="B383" t="n">
+        <v>1150002</v>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="B384" t="n">
+        <v>1150003</v>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Imaginary</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="B385" t="n">
+        <v>111</v>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="B386" t="n">
+        <v>1150003</v>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="B387" t="n">
+        <v>1150002</v>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="B388" t="n">
+        <v>111</v>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="B389" t="n">
+        <v>1150002</v>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="B390" t="n">
+        <v>1150003</v>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="B391" t="n">
+        <v>1150002</v>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>0.4</t>
         </is>
       </c>
     </row>
